--- a/Spellscrolls/RulesApplicationExample.xlsx
+++ b/Spellscrolls/RulesApplicationExample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentmdh-my.sharepoint.com/personal/abs21004_student_mdu_se/Documents/RPG/Return to Farlorret/Spellscrolls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:8000000b_{ACBF3D38-1FC0-483D-A450-C22652F997C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:8000000b_{ACBF3D38-1FC0-483D-A450-C22652F997C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90181123-EA38-4667-838F-1BC51CA9E710}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{712B6D23-A449-45FD-8B49-149B6453368A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{712B6D23-A449-45FD-8B49-149B6453368A}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -615,24 +615,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -669,6 +665,9 @@
         <horizontal/>
       </border>
     </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -691,11 +690,11 @@
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{5F286FC3-BC1C-454E-8F4A-8DC42BEEECBA}" name="Name"/>
     <tableColumn id="2" xr3:uid="{A89229DE-8A33-4D31-ABC5-61C361BC139B}" name="Level"/>
-    <tableColumn id="3" xr3:uid="{85B7ABEB-F27F-4B40-A630-05FEF27EDC19}" name="Components" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{85B7ABEB-F27F-4B40-A630-05FEF27EDC19}" name="Components" dataDxfId="3"/>
     <tableColumn id="4" xr3:uid="{ADA95C41-3A8A-4114-8E3A-75A16C1F8EB4}" name="Consumable Cost"/>
     <tableColumn id="5" xr3:uid="{762BB109-FACD-4C54-AAF4-FC3B6E42E10C}" name="Non-Consumable Cost"/>
-    <tableColumn id="6" xr3:uid="{63F0DAF4-EF04-421C-8BD2-89E001032666}" name="Cost" dataDxfId="3">
-      <calculatedColumnFormula>VLOOKUP(Data!B3,LookupTables!$A$2:$C$11,3)</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{63F0DAF4-EF04-421C-8BD2-89E001032666}" name="Cost" dataDxfId="2">
+      <calculatedColumnFormula>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{ECC71CB1-7F20-480C-B242-C42EBC28C3C0}" name="Time">
       <calculatedColumnFormula>VLOOKUP(F3,LookupTables!$E$2:$F$18,2)</calculatedColumnFormula>
@@ -706,7 +705,7 @@
     <tableColumn id="9" xr3:uid="{7DF4109B-A03C-430C-B895-4B175EE3FB48}" name="Time 50%">
       <calculatedColumnFormula>VLOOKUP(H3,LookupTables!$E$2:$F$18,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{5892B10C-4DCB-41F5-B0FC-11D32C656413}" name="Cost2" dataDxfId="2">
+    <tableColumn id="10" xr3:uid="{5892B10C-4DCB-41F5-B0FC-11D32C656413}" name="Cost2" dataDxfId="1">
       <calculatedColumnFormula>F3+D3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{0823276B-1A68-4883-A7B9-5D905CCE9550}" name="Time3">
@@ -724,7 +723,7 @@
     <tableColumn id="15" xr3:uid="{E3014532-18B2-4A87-8462-846199E14AA4}" name="Time Base 50%">
       <calculatedColumnFormula>VLOOKUP(N3,LookupTables!$E$2:$F$18,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{4807FE2B-5FD9-48A9-84B3-B9E2AC68546B}" name="Cost4" dataDxfId="1">
+    <tableColumn id="16" xr3:uid="{4807FE2B-5FD9-48A9-84B3-B9E2AC68546B}" name="Cost4" dataDxfId="0">
       <calculatedColumnFormula>F3+E3+D3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="17" xr3:uid="{6A5A75C7-5428-45E9-BF4B-8ED505B086F0}" name="Time5">
@@ -1095,47 +1094,47 @@
     <col min="3" max="3" width="68.28515625" customWidth="1"/>
     <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="17" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1" t="s">
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -1147,13 +1146,13 @@
       <c r="C2" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>149</v>
       </c>
       <c r="G2" t="s">
@@ -1162,10 +1161,10 @@
       <c r="H2" t="s">
         <v>151</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>172</v>
       </c>
       <c r="K2" t="s">
@@ -1180,10 +1179,10 @@
       <c r="N2" t="s">
         <v>166</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" t="s">
         <v>167</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>174</v>
       </c>
       <c r="Q2" t="s">
@@ -1198,7 +1197,7 @@
       <c r="T2" t="s">
         <v>178</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="U2" t="s">
         <v>179</v>
       </c>
     </row>
@@ -1209,7 +1208,7 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D3">
@@ -1218,8 +1217,8 @@
       <c r="E3">
         <v>5</v>
       </c>
-      <c r="F3" s="2">
-        <f>VLOOKUP(Data!B8,LookupTables!$A$2:$C$11,3)</f>
+      <c r="F3" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
         <v>25</v>
       </c>
       <c r="G3">
@@ -1227,15 +1226,15 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <f>F3/2</f>
+        <f t="shared" ref="H3:H34" si="0">F3/2</f>
         <v>12.5</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3">
         <f>VLOOKUP(H3,LookupTables!$E$2:$F$18,2)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="2">
-        <f>F3+D3</f>
+      <c r="J3" s="1">
+        <f t="shared" ref="J3:J34" si="1">F3+D3</f>
         <v>25</v>
       </c>
       <c r="K3">
@@ -1243,23 +1242,23 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <f>J3/2</f>
+        <f t="shared" ref="L3:L34" si="2">J3/2</f>
         <v>12.5</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3">
         <f>VLOOKUP(L3,LookupTables!$E$2:$F$18,2)</f>
         <v>0</v>
       </c>
       <c r="N3">
-        <f>F3/2+D3</f>
+        <f t="shared" ref="N3:N34" si="3">F3/2+D3</f>
         <v>12.5</v>
       </c>
-      <c r="O3" s="3">
+      <c r="O3">
         <f>VLOOKUP(N3,LookupTables!$E$2:$F$18,2)</f>
         <v>0</v>
       </c>
-      <c r="P3" s="2">
-        <f>F3+E3+D3</f>
+      <c r="P3" s="1">
+        <f t="shared" ref="P3:P34" si="4">F3+E3+D3</f>
         <v>30</v>
       </c>
       <c r="Q3">
@@ -1267,18 +1266,18 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <f>P3/2</f>
+        <f t="shared" ref="R3:R34" si="5">P3/2</f>
         <v>15</v>
       </c>
-      <c r="S3" s="3">
+      <c r="S3">
         <f>VLOOKUP(R3,LookupTables!$E$2:$F$18,2)</f>
         <v>0</v>
       </c>
       <c r="T3">
-        <f>F3/2+E3+D3</f>
+        <f t="shared" ref="T3:T34" si="6">F3/2+E3+D3</f>
         <v>17.5</v>
       </c>
-      <c r="U3" s="3">
+      <c r="U3">
         <f>VLOOKUP(T3,LookupTables!$E$2:$F$18,2)</f>
         <v>0</v>
       </c>
@@ -1290,7 +1289,7 @@
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>83</v>
       </c>
       <c r="D4">
@@ -1299,69 +1298,69 @@
       <c r="E4">
         <v>50</v>
       </c>
-      <c r="F4" s="2">
-        <f>VLOOKUP(Data!B9,LookupTables!$A$2:$C$11,3)</f>
-        <v>250</v>
+      <c r="F4" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>25</v>
       </c>
       <c r="G4">
         <f>VLOOKUP(F4,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <f>F4/2</f>
-        <v>125</v>
-      </c>
-      <c r="I4" s="3">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+      <c r="I4">
         <f>VLOOKUP(H4,LookupTables!$E$2:$F$18,2)</f>
-        <v>1</v>
-      </c>
-      <c r="J4" s="2">
-        <f>F4+D4</f>
-        <v>250</v>
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
       <c r="K4">
         <f>VLOOKUP(J4,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <f>J4/2</f>
-        <v>125</v>
-      </c>
-      <c r="M4" s="3">
+        <f t="shared" si="2"/>
+        <v>12.5</v>
+      </c>
+      <c r="M4">
         <f>VLOOKUP(L4,LookupTables!$E$2:$F$18,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <f>F4/2+D4</f>
-        <v>125</v>
-      </c>
-      <c r="O4" s="3">
+        <f t="shared" si="3"/>
+        <v>12.5</v>
+      </c>
+      <c r="O4">
         <f>VLOOKUP(N4,LookupTables!$E$2:$F$18,2)</f>
-        <v>1</v>
-      </c>
-      <c r="P4" s="2">
-        <f>F4+E4+D4</f>
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="P4" s="1">
+        <f t="shared" si="4"/>
+        <v>75</v>
       </c>
       <c r="Q4">
         <f>VLOOKUP(P4,LookupTables!$E$2:$F$18,2)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <f>P4/2</f>
-        <v>150</v>
-      </c>
-      <c r="S4" s="3">
+        <f t="shared" si="5"/>
+        <v>37.5</v>
+      </c>
+      <c r="S4">
         <f>VLOOKUP(R4,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <f>F4/2+E4+D4</f>
-        <v>175</v>
-      </c>
-      <c r="U4" s="3">
+        <f t="shared" si="6"/>
+        <v>62.5</v>
+      </c>
+      <c r="U4">
         <f>VLOOKUP(T4,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.2">
@@ -1371,7 +1370,7 @@
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D5">
@@ -1380,69 +1379,69 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="2">
-        <f>VLOOKUP(Data!B21,LookupTables!$A$2:$C$11,3)</f>
-        <v>500</v>
+      <c r="F5" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>25</v>
       </c>
       <c r="G5">
         <f>VLOOKUP(F5,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <f>F5/2</f>
-        <v>250</v>
-      </c>
-      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+      <c r="I5">
         <f>VLOOKUP(H5,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
-      </c>
-      <c r="J5" s="2">
-        <f>F5+D5</f>
-        <v>510</v>
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <f t="shared" si="1"/>
+        <v>35</v>
       </c>
       <c r="K5">
         <f>VLOOKUP(J5,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <f>J5/2</f>
-        <v>255</v>
-      </c>
-      <c r="M5" s="3">
+        <f t="shared" si="2"/>
+        <v>17.5</v>
+      </c>
+      <c r="M5">
         <f>VLOOKUP(L5,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <f>F5/2+D5</f>
-        <v>260</v>
-      </c>
-      <c r="O5" s="3">
+        <f t="shared" si="3"/>
+        <v>22.5</v>
+      </c>
+      <c r="O5">
         <f>VLOOKUP(N5,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
-      </c>
-      <c r="P5" s="2">
-        <f>F5+E5+D5</f>
-        <v>510</v>
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
+        <f t="shared" si="4"/>
+        <v>35</v>
       </c>
       <c r="Q5">
         <f>VLOOKUP(P5,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <f>P5/2</f>
-        <v>255</v>
-      </c>
-      <c r="S5" s="3">
+        <f t="shared" si="5"/>
+        <v>17.5</v>
+      </c>
+      <c r="S5">
         <f>VLOOKUP(R5,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <f>F5/2+E5+D5</f>
-        <v>260</v>
-      </c>
-      <c r="U5" s="3">
+        <f t="shared" si="6"/>
+        <v>22.5</v>
+      </c>
+      <c r="U5">
         <f>VLOOKUP(T5,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.2">
@@ -1452,7 +1451,7 @@
       <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>107</v>
       </c>
       <c r="D6">
@@ -1461,69 +1460,69 @@
       <c r="E6">
         <v>100</v>
       </c>
-      <c r="F6" s="2">
-        <f>VLOOKUP(Data!B33,LookupTables!$A$2:$C$11,3)</f>
-        <v>5000</v>
+      <c r="F6" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>25</v>
       </c>
       <c r="G6">
         <f>VLOOKUP(F6,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <f>F6/2</f>
-        <v>2500</v>
-      </c>
-      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+      <c r="I6">
         <f>VLOOKUP(H6,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="J6" s="2">
-        <f>F6+D6</f>
-        <v>5000</v>
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
       <c r="K6">
         <f>VLOOKUP(J6,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <f>J6/2</f>
-        <v>2500</v>
-      </c>
-      <c r="M6" s="3">
+        <f t="shared" si="2"/>
+        <v>12.5</v>
+      </c>
+      <c r="M6">
         <f>VLOOKUP(L6,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <f>F6/2+D6</f>
-        <v>2500</v>
-      </c>
-      <c r="O6" s="3">
+        <f t="shared" si="3"/>
+        <v>12.5</v>
+      </c>
+      <c r="O6">
         <f>VLOOKUP(N6,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="P6" s="2">
-        <f>F6+E6+D6</f>
-        <v>5100</v>
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <f t="shared" si="4"/>
+        <v>125</v>
       </c>
       <c r="Q6">
         <f>VLOOKUP(P6,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="R6">
-        <f>P6/2</f>
-        <v>2550</v>
-      </c>
-      <c r="S6" s="3">
+        <f t="shared" si="5"/>
+        <v>62.5</v>
+      </c>
+      <c r="S6">
         <f>VLOOKUP(R6,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="T6">
-        <f>F6/2+E6+D6</f>
-        <v>2600</v>
-      </c>
-      <c r="U6" s="3">
+        <f t="shared" si="6"/>
+        <v>112.5</v>
+      </c>
+      <c r="U6">
         <f>VLOOKUP(T6,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.2">
@@ -1533,7 +1532,7 @@
       <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>108</v>
       </c>
       <c r="D7">
@@ -1542,69 +1541,69 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" s="2">
-        <f>VLOOKUP(Data!B34,LookupTables!$A$2:$C$11,3)</f>
-        <v>5000</v>
+      <c r="F7" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>25</v>
       </c>
       <c r="G7">
         <f>VLOOKUP(F7,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <f>F7/2</f>
-        <v>2500</v>
-      </c>
-      <c r="I7" s="3">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+      <c r="I7">
         <f>VLOOKUP(H7,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="J7" s="2">
-        <f>F7+D7</f>
-        <v>5010</v>
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" si="1"/>
+        <v>35</v>
       </c>
       <c r="K7">
         <f>VLOOKUP(J7,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <f>J7/2</f>
-        <v>2505</v>
-      </c>
-      <c r="M7" s="3">
+        <f t="shared" si="2"/>
+        <v>17.5</v>
+      </c>
+      <c r="M7">
         <f>VLOOKUP(L7,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <f>F7/2+D7</f>
-        <v>2510</v>
-      </c>
-      <c r="O7" s="3">
+        <f t="shared" si="3"/>
+        <v>22.5</v>
+      </c>
+      <c r="O7">
         <f>VLOOKUP(N7,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="P7" s="2">
-        <f>F7+E7+D7</f>
-        <v>5010</v>
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <f t="shared" si="4"/>
+        <v>35</v>
       </c>
       <c r="Q7">
         <f>VLOOKUP(P7,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <f>P7/2</f>
-        <v>2505</v>
-      </c>
-      <c r="S7" s="3">
+        <f t="shared" si="5"/>
+        <v>17.5</v>
+      </c>
+      <c r="S7">
         <f>VLOOKUP(R7,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <f>F7/2+E7+D7</f>
-        <v>2510</v>
-      </c>
-      <c r="U7" s="3">
+        <f t="shared" si="6"/>
+        <v>22.5</v>
+      </c>
+      <c r="U7">
         <f>VLOOKUP(T7,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.2">
@@ -1614,7 +1613,7 @@
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>123</v>
       </c>
       <c r="D8">
@@ -1623,69 +1622,69 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" s="2">
-        <f>VLOOKUP(Data!B49,LookupTables!$A$2:$C$11,3)</f>
-        <v>15000</v>
+      <c r="F8" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>25</v>
       </c>
       <c r="G8">
         <f>VLOOKUP(F8,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <f>F8/2</f>
-        <v>7500</v>
-      </c>
-      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+      <c r="I8">
         <f>VLOOKUP(H8,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="J8" s="2">
-        <f>F8+D8</f>
-        <v>15025</v>
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
       <c r="K8">
         <f>VLOOKUP(J8,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <f>J8/2</f>
-        <v>7512.5</v>
-      </c>
-      <c r="M8" s="3">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="M8">
         <f>VLOOKUP(L8,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <f>F8/2+D8</f>
-        <v>7525</v>
-      </c>
-      <c r="O8" s="3">
+        <f t="shared" si="3"/>
+        <v>37.5</v>
+      </c>
+      <c r="O8">
         <f>VLOOKUP(N8,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="P8" s="2">
-        <f>F8+E8+D8</f>
-        <v>15025</v>
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="Q8">
         <f>VLOOKUP(P8,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <f>P8/2</f>
-        <v>7512.5</v>
-      </c>
-      <c r="S8" s="3">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+      <c r="S8">
         <f>VLOOKUP(R8,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <f>F8/2+E8+D8</f>
-        <v>7525</v>
-      </c>
-      <c r="U8" s="3">
+        <f t="shared" si="6"/>
+        <v>37.5</v>
+      </c>
+      <c r="U8">
         <f>VLOOKUP(T8,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.2">
@@ -1695,7 +1694,7 @@
       <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D9">
@@ -1704,69 +1703,69 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="2">
-        <f>VLOOKUP(Data!B4,LookupTables!$A$2:$C$11,3)</f>
-        <v>25</v>
+      <c r="F9" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>250</v>
       </c>
       <c r="G9">
         <f>VLOOKUP(F9,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <f>F9/2</f>
-        <v>12.5</v>
-      </c>
-      <c r="I9" s="3">
+        <f t="shared" si="0"/>
+        <v>125</v>
+      </c>
+      <c r="I9">
         <f>VLOOKUP(H9,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
-        <f>F9+D9</f>
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" si="1"/>
+        <v>275</v>
       </c>
       <c r="K9">
         <f>VLOOKUP(J9,LookupTables!$E$2:$F$18,2)</f>
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="2"/>
+        <v>137.5</v>
+      </c>
+      <c r="M9">
+        <f>VLOOKUP(L9,LookupTables!$E$2:$F$18,2)</f>
         <v>1</v>
       </c>
-      <c r="L9">
-        <f>J9/2</f>
-        <v>25</v>
-      </c>
-      <c r="M9" s="3">
-        <f>VLOOKUP(L9,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
-      </c>
       <c r="N9">
-        <f>F9/2+D9</f>
-        <v>37.5</v>
-      </c>
-      <c r="O9" s="3">
+        <f t="shared" si="3"/>
+        <v>150</v>
+      </c>
+      <c r="O9">
         <f>VLOOKUP(N9,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
-      </c>
-      <c r="P9" s="2">
-        <f>F9+E9+D9</f>
-        <v>50</v>
+        <v>3</v>
+      </c>
+      <c r="P9" s="1">
+        <f t="shared" si="4"/>
+        <v>275</v>
       </c>
       <c r="Q9">
         <f>VLOOKUP(P9,LookupTables!$E$2:$F$18,2)</f>
+        <v>3</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="5"/>
+        <v>137.5</v>
+      </c>
+      <c r="S9">
+        <f>VLOOKUP(R9,LookupTables!$E$2:$F$18,2)</f>
         <v>1</v>
       </c>
-      <c r="R9">
-        <f>P9/2</f>
-        <v>25</v>
-      </c>
-      <c r="S9" s="3">
-        <f>VLOOKUP(R9,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
-      </c>
       <c r="T9">
-        <f>F9/2+E9+D9</f>
-        <v>37.5</v>
-      </c>
-      <c r="U9" s="3">
+        <f t="shared" si="6"/>
+        <v>150</v>
+      </c>
+      <c r="U9">
         <f>VLOOKUP(T9,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
@@ -1776,7 +1775,7 @@
       <c r="B10">
         <v>2</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D10">
@@ -1785,69 +1784,69 @@
       <c r="E10">
         <v>25</v>
       </c>
-      <c r="F10" s="2">
-        <f>VLOOKUP(Data!B6,LookupTables!$A$2:$C$11,3)</f>
-        <v>25</v>
+      <c r="F10" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>250</v>
       </c>
       <c r="G10">
         <f>VLOOKUP(F10,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10">
-        <f>F10/2</f>
-        <v>12.5</v>
-      </c>
-      <c r="I10" s="3">
+        <f t="shared" si="0"/>
+        <v>125</v>
+      </c>
+      <c r="I10">
         <f>VLOOKUP(H10,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="2">
-        <f>F10+D10</f>
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="J10" s="1">
+        <f t="shared" si="1"/>
+        <v>250</v>
       </c>
       <c r="K10">
         <f>VLOOKUP(J10,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L10">
-        <f>J10/2</f>
-        <v>12.5</v>
-      </c>
-      <c r="M10" s="3">
+        <f t="shared" si="2"/>
+        <v>125</v>
+      </c>
+      <c r="M10">
         <f>VLOOKUP(L10,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10">
-        <f>F10/2+D10</f>
-        <v>12.5</v>
-      </c>
-      <c r="O10" s="3">
+        <f t="shared" si="3"/>
+        <v>125</v>
+      </c>
+      <c r="O10">
         <f>VLOOKUP(N10,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
-      </c>
-      <c r="P10" s="2">
-        <f>F10+E10+D10</f>
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="P10" s="1">
+        <f t="shared" si="4"/>
+        <v>275</v>
       </c>
       <c r="Q10">
         <f>VLOOKUP(P10,LookupTables!$E$2:$F$18,2)</f>
+        <v>3</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="5"/>
+        <v>137.5</v>
+      </c>
+      <c r="S10">
+        <f>VLOOKUP(R10,LookupTables!$E$2:$F$18,2)</f>
         <v>1</v>
       </c>
-      <c r="R10">
-        <f>P10/2</f>
-        <v>25</v>
-      </c>
-      <c r="S10" s="3">
-        <f>VLOOKUP(R10,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
-      </c>
       <c r="T10">
-        <f>F10/2+E10+D10</f>
-        <v>37.5</v>
-      </c>
-      <c r="U10" s="3">
+        <f t="shared" si="6"/>
+        <v>150</v>
+      </c>
+      <c r="U10">
         <f>VLOOKUP(T10,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.2">
@@ -1857,7 +1856,7 @@
       <c r="B11">
         <v>2</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D11">
@@ -1866,8 +1865,8 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" s="2">
-        <f>VLOOKUP(Data!B14,LookupTables!$A$2:$C$11,3)</f>
+      <c r="F11" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
         <v>250</v>
       </c>
       <c r="G11">
@@ -1875,15 +1874,15 @@
         <v>3</v>
       </c>
       <c r="H11">
-        <f>F11/2</f>
+        <f t="shared" si="0"/>
         <v>125</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11">
         <f>VLOOKUP(H11,LookupTables!$E$2:$F$18,2)</f>
         <v>1</v>
       </c>
-      <c r="J11" s="2">
-        <f>F11+D11</f>
+      <c r="J11" s="1">
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="K11">
@@ -1891,23 +1890,23 @@
         <v>5</v>
       </c>
       <c r="L11">
-        <f>J11/2</f>
+        <f t="shared" si="2"/>
         <v>150</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11">
         <f>VLOOKUP(L11,LookupTables!$E$2:$F$18,2)</f>
         <v>3</v>
       </c>
       <c r="N11">
-        <f>F11/2+D11</f>
+        <f t="shared" si="3"/>
         <v>175</v>
       </c>
-      <c r="O11" s="3">
+      <c r="O11">
         <f>VLOOKUP(N11,LookupTables!$E$2:$F$18,2)</f>
         <v>3</v>
       </c>
-      <c r="P11" s="2">
-        <f>F11+E11+D11</f>
+      <c r="P11" s="1">
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="Q11">
@@ -1915,18 +1914,18 @@
         <v>5</v>
       </c>
       <c r="R11">
-        <f>P11/2</f>
+        <f t="shared" si="5"/>
         <v>150</v>
       </c>
-      <c r="S11" s="3">
+      <c r="S11">
         <f>VLOOKUP(R11,LookupTables!$E$2:$F$18,2)</f>
         <v>3</v>
       </c>
       <c r="T11">
-        <f>F11/2+E11+D11</f>
+        <f t="shared" si="6"/>
         <v>175</v>
       </c>
-      <c r="U11" s="3">
+      <c r="U11">
         <f>VLOOKUP(T11,LookupTables!$E$2:$F$18,2)</f>
         <v>3</v>
       </c>
@@ -1938,7 +1937,7 @@
       <c r="B12">
         <v>2</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>90</v>
       </c>
       <c r="D12">
@@ -1947,8 +1946,8 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="2">
-        <f>VLOOKUP(Data!B16,LookupTables!$A$2:$C$11,3)</f>
+      <c r="F12" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
         <v>250</v>
       </c>
       <c r="G12">
@@ -1956,15 +1955,15 @@
         <v>3</v>
       </c>
       <c r="H12">
-        <f>F12/2</f>
+        <f t="shared" si="0"/>
         <v>125</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12">
         <f>VLOOKUP(H12,LookupTables!$E$2:$F$18,2)</f>
         <v>1</v>
       </c>
-      <c r="J12" s="2">
-        <f>F12+D12</f>
+      <c r="J12" s="1">
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="K12">
@@ -1972,23 +1971,23 @@
         <v>5</v>
       </c>
       <c r="L12">
-        <f>J12/2</f>
+        <f t="shared" si="2"/>
         <v>150</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12">
         <f>VLOOKUP(L12,LookupTables!$E$2:$F$18,2)</f>
         <v>3</v>
       </c>
       <c r="N12">
-        <f>F12/2+D12</f>
+        <f t="shared" si="3"/>
         <v>175</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12">
         <f>VLOOKUP(N12,LookupTables!$E$2:$F$18,2)</f>
         <v>3</v>
       </c>
-      <c r="P12" s="2">
-        <f>F12+E12+D12</f>
+      <c r="P12" s="1">
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="Q12">
@@ -1996,18 +1995,18 @@
         <v>5</v>
       </c>
       <c r="R12">
-        <f>P12/2</f>
+        <f t="shared" si="5"/>
         <v>150</v>
       </c>
-      <c r="S12" s="3">
+      <c r="S12">
         <f>VLOOKUP(R12,LookupTables!$E$2:$F$18,2)</f>
         <v>3</v>
       </c>
       <c r="T12">
-        <f>F12/2+E12+D12</f>
+        <f t="shared" si="6"/>
         <v>175</v>
       </c>
-      <c r="U12" s="3">
+      <c r="U12">
         <f>VLOOKUP(T12,LookupTables!$E$2:$F$18,2)</f>
         <v>3</v>
       </c>
@@ -2019,7 +2018,7 @@
       <c r="B13">
         <v>2</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D13">
@@ -2028,8 +2027,8 @@
       <c r="E13" t="s">
         <v>169</v>
       </c>
-      <c r="F13" s="2">
-        <f>VLOOKUP(Data!B17,LookupTables!$A$2:$C$11,3)</f>
+      <c r="F13" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
         <v>250</v>
       </c>
       <c r="G13">
@@ -2037,15 +2036,15 @@
         <v>3</v>
       </c>
       <c r="H13">
-        <f>F13/2</f>
+        <f t="shared" si="0"/>
         <v>125</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13">
         <f>VLOOKUP(H13,LookupTables!$E$2:$F$18,2)</f>
         <v>1</v>
       </c>
-      <c r="J13" s="2">
-        <f>F13+D13</f>
+      <c r="J13" s="1">
+        <f t="shared" si="1"/>
         <v>350</v>
       </c>
       <c r="K13">
@@ -2053,23 +2052,23 @@
         <v>5</v>
       </c>
       <c r="L13">
-        <f>J13/2</f>
+        <f t="shared" si="2"/>
         <v>175</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M13">
         <f>VLOOKUP(L13,LookupTables!$E$2:$F$18,2)</f>
         <v>3</v>
       </c>
       <c r="N13">
-        <f>F13/2+D13</f>
+        <f t="shared" si="3"/>
         <v>225</v>
       </c>
-      <c r="O13" s="3">
+      <c r="O13">
         <f>VLOOKUP(N13,LookupTables!$E$2:$F$18,2)</f>
         <v>3</v>
       </c>
-      <c r="P13" s="2" t="e">
-        <f>F13+E13+D13</f>
+      <c r="P13" s="1" t="e">
+        <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
       <c r="Q13" t="e">
@@ -2077,18 +2076,18 @@
         <v>#VALUE!</v>
       </c>
       <c r="R13" t="e">
-        <f>P13/2</f>
+        <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S13" s="3" t="e">
+      <c r="S13" t="e">
         <f>VLOOKUP(R13,LookupTables!$E$2:$F$18,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="T13" t="e">
-        <f>F13/2+E13+D13</f>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
-      <c r="U13" s="3" t="e">
+      <c r="U13" t="e">
         <f>VLOOKUP(T13,LookupTables!$E$2:$F$18,2)</f>
         <v>#VALUE!</v>
       </c>
@@ -2100,7 +2099,7 @@
       <c r="B14">
         <v>2</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>106</v>
       </c>
       <c r="D14">
@@ -2109,69 +2108,69 @@
       <c r="E14">
         <v>100</v>
       </c>
-      <c r="F14" s="2">
-        <f>VLOOKUP(Data!B32,LookupTables!$A$2:$C$11,3)</f>
-        <v>5000</v>
+      <c r="F14" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>250</v>
       </c>
       <c r="G14">
         <f>VLOOKUP(F14,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <f>F14/2</f>
-        <v>2500</v>
-      </c>
-      <c r="I14" s="3">
+        <f t="shared" si="0"/>
+        <v>125</v>
+      </c>
+      <c r="I14">
         <f>VLOOKUP(H14,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="J14" s="2">
-        <f>F14+D14</f>
-        <v>5000</v>
+        <v>1</v>
+      </c>
+      <c r="J14" s="1">
+        <f t="shared" si="1"/>
+        <v>250</v>
       </c>
       <c r="K14">
         <f>VLOOKUP(J14,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="L14">
-        <f>J14/2</f>
-        <v>2500</v>
-      </c>
-      <c r="M14" s="3">
+        <f t="shared" si="2"/>
+        <v>125</v>
+      </c>
+      <c r="M14">
         <f>VLOOKUP(L14,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="N14">
-        <f>F14/2+D14</f>
-        <v>2500</v>
-      </c>
-      <c r="O14" s="3">
+        <f t="shared" si="3"/>
+        <v>125</v>
+      </c>
+      <c r="O14">
         <f>VLOOKUP(N14,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="P14" s="2">
-        <f>F14+E14+D14</f>
-        <v>5100</v>
+        <v>1</v>
+      </c>
+      <c r="P14" s="1">
+        <f t="shared" si="4"/>
+        <v>350</v>
       </c>
       <c r="Q14">
         <f>VLOOKUP(P14,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <f>P14/2</f>
-        <v>2550</v>
-      </c>
-      <c r="S14" s="3">
+        <f t="shared" si="5"/>
+        <v>175</v>
+      </c>
+      <c r="S14">
         <f>VLOOKUP(R14,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="T14">
-        <f>F14/2+E14+D14</f>
-        <v>2600</v>
-      </c>
-      <c r="U14" s="3">
+        <f t="shared" si="6"/>
+        <v>225</v>
+      </c>
+      <c r="U14">
         <f>VLOOKUP(T14,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
@@ -2181,7 +2180,7 @@
       <c r="B15">
         <v>2</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D15">
@@ -2190,69 +2189,69 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="2">
-        <f>VLOOKUP(Data!B41,LookupTables!$A$2:$C$11,3)</f>
-        <v>5000</v>
+      <c r="F15" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>250</v>
       </c>
       <c r="G15">
         <f>VLOOKUP(F15,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <f>F15/2</f>
-        <v>2500</v>
-      </c>
-      <c r="I15" s="3">
+        <f t="shared" si="0"/>
+        <v>125</v>
+      </c>
+      <c r="I15">
         <f>VLOOKUP(H15,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="J15" s="2">
-        <f>F15+D15</f>
-        <v>5010</v>
+        <v>1</v>
+      </c>
+      <c r="J15" s="1">
+        <f t="shared" si="1"/>
+        <v>260</v>
       </c>
       <c r="K15">
         <f>VLOOKUP(J15,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="L15">
-        <f>J15/2</f>
-        <v>2505</v>
-      </c>
-      <c r="M15" s="3">
+        <f t="shared" si="2"/>
+        <v>130</v>
+      </c>
+      <c r="M15">
         <f>VLOOKUP(L15,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="N15">
-        <f>F15/2+D15</f>
-        <v>2510</v>
-      </c>
-      <c r="O15" s="3">
+        <f t="shared" si="3"/>
+        <v>135</v>
+      </c>
+      <c r="O15">
         <f>VLOOKUP(N15,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="P15" s="2">
-        <f>F15+E15+D15</f>
-        <v>5010</v>
+        <v>1</v>
+      </c>
+      <c r="P15" s="1">
+        <f t="shared" si="4"/>
+        <v>260</v>
       </c>
       <c r="Q15">
         <f>VLOOKUP(P15,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="R15">
-        <f>P15/2</f>
-        <v>2505</v>
-      </c>
-      <c r="S15" s="3">
+        <f t="shared" si="5"/>
+        <v>130</v>
+      </c>
+      <c r="S15">
         <f>VLOOKUP(R15,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="T15">
-        <f>F15/2+E15+D15</f>
-        <v>2510</v>
-      </c>
-      <c r="U15" s="3">
+        <f t="shared" si="6"/>
+        <v>135</v>
+      </c>
+      <c r="U15">
         <f>VLOOKUP(T15,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
@@ -2262,7 +2261,7 @@
       <c r="B16">
         <v>2</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="2" t="s">
         <v>133</v>
       </c>
       <c r="D16">
@@ -2271,69 +2270,69 @@
       <c r="E16">
         <v>200</v>
       </c>
-      <c r="F16" s="2">
-        <f>VLOOKUP(Data!B61,LookupTables!$A$2:$C$11,3)</f>
-        <v>25000</v>
+      <c r="F16" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>250</v>
       </c>
       <c r="G16">
         <f>VLOOKUP(F16,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H16">
-        <f>F16/2</f>
-        <v>12500</v>
-      </c>
-      <c r="I16" s="3">
+        <f t="shared" si="0"/>
+        <v>125</v>
+      </c>
+      <c r="I16">
         <f>VLOOKUP(H16,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
-      </c>
-      <c r="J16" s="2">
-        <f>F16+D16</f>
-        <v>25000</v>
+        <v>1</v>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" si="1"/>
+        <v>250</v>
       </c>
       <c r="K16">
         <f>VLOOKUP(J16,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="L16">
-        <f>J16/2</f>
-        <v>12500</v>
-      </c>
-      <c r="M16" s="3">
+        <f t="shared" si="2"/>
+        <v>125</v>
+      </c>
+      <c r="M16">
         <f>VLOOKUP(L16,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="N16">
-        <f>F16/2+D16</f>
-        <v>12500</v>
-      </c>
-      <c r="O16" s="3">
+        <f t="shared" si="3"/>
+        <v>125</v>
+      </c>
+      <c r="O16">
         <f>VLOOKUP(N16,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
-      </c>
-      <c r="P16" s="2">
-        <f>F16+E16+D16</f>
-        <v>25200</v>
+        <v>1</v>
+      </c>
+      <c r="P16" s="1">
+        <f t="shared" si="4"/>
+        <v>450</v>
       </c>
       <c r="Q16">
         <f>VLOOKUP(P16,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <f>P16/2</f>
-        <v>12600</v>
-      </c>
-      <c r="S16" s="3">
+        <f t="shared" si="5"/>
+        <v>225</v>
+      </c>
+      <c r="S16">
         <f>VLOOKUP(R16,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="T16">
-        <f>F16/2+E16+D16</f>
-        <v>12700</v>
-      </c>
-      <c r="U16" s="3">
+        <f t="shared" si="6"/>
+        <v>325</v>
+      </c>
+      <c r="U16">
         <f>VLOOKUP(T16,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
@@ -2343,7 +2342,7 @@
       <c r="B17">
         <v>2</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="2" t="s">
         <v>147</v>
       </c>
       <c r="D17">
@@ -2352,69 +2351,69 @@
       <c r="E17">
         <v>100</v>
       </c>
-      <c r="F17" s="2">
-        <f>VLOOKUP(Data!B75,LookupTables!$A$2:$C$11,3)</f>
-        <v>250000</v>
+      <c r="F17" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>250</v>
       </c>
       <c r="G17">
         <f>VLOOKUP(F17,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H17">
-        <f>F17/2</f>
-        <v>125000</v>
-      </c>
-      <c r="I17" s="3">
+        <f t="shared" si="0"/>
+        <v>125</v>
+      </c>
+      <c r="I17">
         <f>VLOOKUP(H17,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
-      </c>
-      <c r="J17" s="2">
-        <f>F17+D17</f>
-        <v>250000</v>
+        <v>1</v>
+      </c>
+      <c r="J17" s="1">
+        <f t="shared" si="1"/>
+        <v>250</v>
       </c>
       <c r="K17">
         <f>VLOOKUP(J17,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="L17">
-        <f>J17/2</f>
-        <v>125000</v>
-      </c>
-      <c r="M17" s="3">
+        <f t="shared" si="2"/>
+        <v>125</v>
+      </c>
+      <c r="M17">
         <f>VLOOKUP(L17,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="N17">
-        <f>F17/2+D17</f>
-        <v>125000</v>
-      </c>
-      <c r="O17" s="3">
+        <f t="shared" si="3"/>
+        <v>125</v>
+      </c>
+      <c r="O17">
         <f>VLOOKUP(N17,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
-      </c>
-      <c r="P17" s="2">
-        <f>F17+E17+D17</f>
-        <v>250100</v>
+        <v>1</v>
+      </c>
+      <c r="P17" s="1">
+        <f t="shared" si="4"/>
+        <v>350</v>
       </c>
       <c r="Q17">
         <f>VLOOKUP(P17,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <f>P17/2</f>
-        <v>125050</v>
-      </c>
-      <c r="S17" s="3">
+        <f t="shared" si="5"/>
+        <v>175</v>
+      </c>
+      <c r="S17">
         <f>VLOOKUP(R17,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="T17">
-        <f>F17/2+E17+D17</f>
-        <v>125100</v>
-      </c>
-      <c r="U17" s="3">
+        <f t="shared" si="6"/>
+        <v>225</v>
+      </c>
+      <c r="U17">
         <f>VLOOKUP(T17,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
@@ -2424,7 +2423,7 @@
       <c r="B18">
         <v>3</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="2" t="s">
         <v>85</v>
       </c>
       <c r="D18">
@@ -2433,69 +2432,69 @@
       <c r="E18">
         <v>100</v>
       </c>
-      <c r="F18" s="2">
-        <f>VLOOKUP(Data!B11,LookupTables!$A$2:$C$11,3)</f>
-        <v>250</v>
+      <c r="F18" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>500</v>
       </c>
       <c r="G18">
         <f>VLOOKUP(F18,LookupTables!$E$2:$F$18,2)</f>
+        <v>7</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="I18">
+        <f>VLOOKUP(H18,LookupTables!$E$2:$F$18,2)</f>
         <v>3</v>
       </c>
-      <c r="H18">
-        <f>F18/2</f>
-        <v>125</v>
-      </c>
-      <c r="I18" s="3">
-        <f>VLOOKUP(H18,LookupTables!$E$2:$F$18,2)</f>
-        <v>1</v>
-      </c>
-      <c r="J18" s="2">
-        <f>F18+D18</f>
-        <v>250</v>
+      <c r="J18" s="1">
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="K18">
         <f>VLOOKUP(J18,LookupTables!$E$2:$F$18,2)</f>
+        <v>7</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="2"/>
+        <v>250</v>
+      </c>
+      <c r="M18">
+        <f>VLOOKUP(L18,LookupTables!$E$2:$F$18,2)</f>
         <v>3</v>
       </c>
-      <c r="L18">
-        <f>J18/2</f>
-        <v>125</v>
-      </c>
-      <c r="M18" s="3">
-        <f>VLOOKUP(L18,LookupTables!$E$2:$F$18,2)</f>
-        <v>1</v>
-      </c>
       <c r="N18">
-        <f>F18/2+D18</f>
-        <v>125</v>
-      </c>
-      <c r="O18" s="3">
+        <f t="shared" si="3"/>
+        <v>250</v>
+      </c>
+      <c r="O18">
         <f>VLOOKUP(N18,LookupTables!$E$2:$F$18,2)</f>
-        <v>1</v>
-      </c>
-      <c r="P18" s="2">
-        <f>F18+E18+D18</f>
-        <v>350</v>
+        <v>3</v>
+      </c>
+      <c r="P18" s="1">
+        <f t="shared" si="4"/>
+        <v>600</v>
       </c>
       <c r="Q18">
         <f>VLOOKUP(P18,LookupTables!$E$2:$F$18,2)</f>
+        <v>7</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="5"/>
+        <v>300</v>
+      </c>
+      <c r="S18">
+        <f>VLOOKUP(R18,LookupTables!$E$2:$F$18,2)</f>
         <v>5</v>
       </c>
-      <c r="R18">
-        <f>P18/2</f>
-        <v>175</v>
-      </c>
-      <c r="S18" s="3">
-        <f>VLOOKUP(R18,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
-      </c>
       <c r="T18">
-        <f>F18/2+E18+D18</f>
-        <v>225</v>
-      </c>
-      <c r="U18" s="3">
+        <f t="shared" si="6"/>
+        <v>350</v>
+      </c>
+      <c r="U18">
         <f>VLOOKUP(T18,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.2">
@@ -2505,7 +2504,7 @@
       <c r="B19">
         <v>3</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D19">
@@ -2514,69 +2513,69 @@
       <c r="E19">
         <v>0</v>
       </c>
-      <c r="F19" s="2">
-        <f>VLOOKUP(Data!B26,LookupTables!$A$2:$C$11,3)</f>
-        <v>2500</v>
+      <c r="F19" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>500</v>
       </c>
       <c r="G19">
         <f>VLOOKUP(F19,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H19">
-        <f>F19/2</f>
-        <v>1250</v>
-      </c>
-      <c r="I19" s="3">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="I19">
         <f>VLOOKUP(H19,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
-      </c>
-      <c r="J19" s="2">
-        <f>F19+D19</f>
-        <v>2700</v>
+        <v>3</v>
+      </c>
+      <c r="J19" s="1">
+        <f t="shared" si="1"/>
+        <v>700</v>
       </c>
       <c r="K19">
         <f>VLOOKUP(J19,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <f>J19/2</f>
-        <v>1350</v>
-      </c>
-      <c r="M19" s="3">
+        <f t="shared" si="2"/>
+        <v>350</v>
+      </c>
+      <c r="M19">
         <f>VLOOKUP(L19,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <f>F19/2+D19</f>
-        <v>1450</v>
-      </c>
-      <c r="O19" s="3">
+        <f t="shared" si="3"/>
+        <v>450</v>
+      </c>
+      <c r="O19">
         <f>VLOOKUP(N19,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
-      </c>
-      <c r="P19" s="2">
-        <f>F19+E19+D19</f>
-        <v>2700</v>
+        <v>7</v>
+      </c>
+      <c r="P19" s="1">
+        <f t="shared" si="4"/>
+        <v>700</v>
       </c>
       <c r="Q19">
         <f>VLOOKUP(P19,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <f>P19/2</f>
-        <v>1350</v>
-      </c>
-      <c r="S19" s="3">
+        <f t="shared" si="5"/>
+        <v>350</v>
+      </c>
+      <c r="S19">
         <f>VLOOKUP(R19,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T19">
-        <f>F19/2+E19+D19</f>
-        <v>1450</v>
-      </c>
-      <c r="U19" s="3">
+        <f t="shared" si="6"/>
+        <v>450</v>
+      </c>
+      <c r="U19">
         <f>VLOOKUP(T19,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.2">
@@ -2586,7 +2585,7 @@
       <c r="B20">
         <v>3</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D20">
@@ -2595,69 +2594,69 @@
       <c r="E20">
         <v>250</v>
       </c>
-      <c r="F20" s="2">
-        <f>VLOOKUP(Data!B36,LookupTables!$A$2:$C$11,3)</f>
-        <v>5000</v>
+      <c r="F20" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>500</v>
       </c>
       <c r="G20">
         <f>VLOOKUP(F20,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="H20">
-        <f>F20/2</f>
-        <v>2500</v>
-      </c>
-      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="I20">
         <f>VLOOKUP(H20,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="J20" s="2">
-        <f>F20+D20</f>
-        <v>5000</v>
+        <v>3</v>
+      </c>
+      <c r="J20" s="1">
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="K20">
         <f>VLOOKUP(J20,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="L20">
-        <f>J20/2</f>
-        <v>2500</v>
-      </c>
-      <c r="M20" s="3">
+        <f t="shared" si="2"/>
+        <v>250</v>
+      </c>
+      <c r="M20">
         <f>VLOOKUP(L20,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="N20">
-        <f>F20/2+D20</f>
-        <v>2500</v>
-      </c>
-      <c r="O20" s="3">
+        <f t="shared" si="3"/>
+        <v>250</v>
+      </c>
+      <c r="O20">
         <f>VLOOKUP(N20,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="P20" s="2">
-        <f>F20+E20+D20</f>
-        <v>5250</v>
+        <v>3</v>
+      </c>
+      <c r="P20" s="1">
+        <f t="shared" si="4"/>
+        <v>750</v>
       </c>
       <c r="Q20">
         <f>VLOOKUP(P20,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <f>P20/2</f>
-        <v>2625</v>
-      </c>
-      <c r="S20" s="3">
+        <f t="shared" si="5"/>
+        <v>375</v>
+      </c>
+      <c r="S20">
         <f>VLOOKUP(R20,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T20">
-        <f>F20/2+E20+D20</f>
-        <v>2750</v>
-      </c>
-      <c r="U20" s="3">
+        <f t="shared" si="6"/>
+        <v>500</v>
+      </c>
+      <c r="U20">
         <f>VLOOKUP(T20,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.2">
@@ -2667,7 +2666,7 @@
       <c r="B21">
         <v>3</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="2" t="s">
         <v>113</v>
       </c>
       <c r="D21">
@@ -2676,69 +2675,69 @@
       <c r="E21">
         <v>0</v>
       </c>
-      <c r="F21" s="2">
-        <f>VLOOKUP(Data!B39,LookupTables!$A$2:$C$11,3)</f>
-        <v>5000</v>
+      <c r="F21" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>500</v>
       </c>
       <c r="G21">
         <f>VLOOKUP(F21,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="H21">
-        <f>F21/2</f>
-        <v>2500</v>
-      </c>
-      <c r="I21" s="3">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="I21">
         <f>VLOOKUP(H21,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="J21" s="2">
-        <f>F21+D21</f>
-        <v>5100</v>
+        <v>3</v>
+      </c>
+      <c r="J21" s="1">
+        <f t="shared" si="1"/>
+        <v>600</v>
       </c>
       <c r="K21">
         <f>VLOOKUP(J21,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="L21">
-        <f>J21/2</f>
-        <v>2550</v>
-      </c>
-      <c r="M21" s="3">
+        <f t="shared" si="2"/>
+        <v>300</v>
+      </c>
+      <c r="M21">
         <f>VLOOKUP(L21,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <f>F21/2+D21</f>
-        <v>2600</v>
-      </c>
-      <c r="O21" s="3">
+        <f t="shared" si="3"/>
+        <v>350</v>
+      </c>
+      <c r="O21">
         <f>VLOOKUP(N21,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="P21" s="2">
-        <f>F21+E21+D21</f>
-        <v>5100</v>
+        <v>5</v>
+      </c>
+      <c r="P21" s="1">
+        <f t="shared" si="4"/>
+        <v>600</v>
       </c>
       <c r="Q21">
         <f>VLOOKUP(P21,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <f>P21/2</f>
-        <v>2550</v>
-      </c>
-      <c r="S21" s="3">
+        <f t="shared" si="5"/>
+        <v>300</v>
+      </c>
+      <c r="S21">
         <f>VLOOKUP(R21,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T21">
-        <f>F21/2+E21+D21</f>
-        <v>2600</v>
-      </c>
-      <c r="U21" s="3">
+        <f t="shared" si="6"/>
+        <v>350</v>
+      </c>
+      <c r="U21">
         <f>VLOOKUP(T21,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.2">
@@ -2748,7 +2747,7 @@
       <c r="B22">
         <v>3</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="2" t="s">
         <v>118</v>
       </c>
       <c r="D22">
@@ -2757,69 +2756,69 @@
       <c r="E22">
         <v>0</v>
       </c>
-      <c r="F22" s="2">
-        <f>VLOOKUP(Data!B44,LookupTables!$A$2:$C$11,3)</f>
-        <v>5000</v>
+      <c r="F22" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>500</v>
       </c>
       <c r="G22">
         <f>VLOOKUP(F22,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="H22">
-        <f>F22/2</f>
-        <v>2500</v>
-      </c>
-      <c r="I22" s="3">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="I22">
         <f>VLOOKUP(H22,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="J22" s="2">
-        <f>F22+D22</f>
-        <v>5025</v>
+        <v>3</v>
+      </c>
+      <c r="J22" s="1">
+        <f t="shared" si="1"/>
+        <v>525</v>
       </c>
       <c r="K22">
         <f>VLOOKUP(J22,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <f>J22/2</f>
-        <v>2512.5</v>
-      </c>
-      <c r="M22" s="3">
+        <f t="shared" si="2"/>
+        <v>262.5</v>
+      </c>
+      <c r="M22">
         <f>VLOOKUP(L22,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="N22">
-        <f>F22/2+D22</f>
-        <v>2525</v>
-      </c>
-      <c r="O22" s="3">
+        <f t="shared" si="3"/>
+        <v>275</v>
+      </c>
+      <c r="O22">
         <f>VLOOKUP(N22,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="P22" s="2">
-        <f>F22+E22+D22</f>
-        <v>5025</v>
+        <v>3</v>
+      </c>
+      <c r="P22" s="1">
+        <f t="shared" si="4"/>
+        <v>525</v>
       </c>
       <c r="Q22">
         <f>VLOOKUP(P22,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="R22">
-        <f>P22/2</f>
-        <v>2512.5</v>
-      </c>
-      <c r="S22" s="3">
+        <f t="shared" si="5"/>
+        <v>262.5</v>
+      </c>
+      <c r="S22">
         <f>VLOOKUP(R22,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="T22">
-        <f>F22/2+E22+D22</f>
-        <v>2525</v>
-      </c>
-      <c r="U22" s="3">
+        <f t="shared" si="6"/>
+        <v>275</v>
+      </c>
+      <c r="U22">
         <f>VLOOKUP(T22,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.2">
@@ -2829,7 +2828,7 @@
       <c r="B23">
         <v>3</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="2" t="s">
         <v>127</v>
       </c>
       <c r="D23">
@@ -2838,69 +2837,69 @@
       <c r="E23">
         <v>0</v>
       </c>
-      <c r="F23" s="2">
-        <f>VLOOKUP(Data!B53,LookupTables!$A$2:$C$11,3)</f>
-        <v>15000</v>
+      <c r="F23" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>500</v>
       </c>
       <c r="G23">
         <f>VLOOKUP(F23,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H23">
-        <f>F23/2</f>
-        <v>7500</v>
-      </c>
-      <c r="I23" s="3">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="I23">
         <f>VLOOKUP(H23,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="J23" s="2">
-        <f>F23+D23</f>
-        <v>15300</v>
+        <v>3</v>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" si="1"/>
+        <v>800</v>
       </c>
       <c r="K23">
         <f>VLOOKUP(J23,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <f>J23/2</f>
-        <v>7650</v>
-      </c>
-      <c r="M23" s="3">
+        <f t="shared" si="2"/>
+        <v>400</v>
+      </c>
+      <c r="M23">
         <f>VLOOKUP(L23,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="N23">
-        <f>F23/2+D23</f>
-        <v>7800</v>
-      </c>
-      <c r="O23" s="3">
+        <f t="shared" si="3"/>
+        <v>550</v>
+      </c>
+      <c r="O23">
         <f>VLOOKUP(N23,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="P23" s="2">
-        <f>F23+E23+D23</f>
-        <v>15300</v>
+        <v>7</v>
+      </c>
+      <c r="P23" s="1">
+        <f t="shared" si="4"/>
+        <v>800</v>
       </c>
       <c r="Q23">
         <f>VLOOKUP(P23,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <f>P23/2</f>
-        <v>7650</v>
-      </c>
-      <c r="S23" s="3">
+        <f t="shared" si="5"/>
+        <v>400</v>
+      </c>
+      <c r="S23">
         <f>VLOOKUP(R23,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="T23">
-        <f>F23/2+E23+D23</f>
-        <v>7800</v>
-      </c>
-      <c r="U23" s="3">
+        <f t="shared" si="6"/>
+        <v>550</v>
+      </c>
+      <c r="U23">
         <f>VLOOKUP(T23,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.2">
@@ -2910,7 +2909,7 @@
       <c r="B24">
         <v>3</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="2" t="s">
         <v>138</v>
       </c>
       <c r="D24">
@@ -2919,69 +2918,69 @@
       <c r="E24">
         <v>300</v>
       </c>
-      <c r="F24" s="2">
-        <f>VLOOKUP(Data!B66,LookupTables!$A$2:$C$11,3)</f>
-        <v>25000</v>
+      <c r="F24" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>500</v>
       </c>
       <c r="G24">
         <f>VLOOKUP(F24,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="H24">
-        <f>F24/2</f>
-        <v>12500</v>
-      </c>
-      <c r="I24" s="3">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="I24">
         <f>VLOOKUP(H24,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
-      </c>
-      <c r="J24" s="2">
-        <f>F24+D24</f>
-        <v>25000</v>
+        <v>3</v>
+      </c>
+      <c r="J24" s="1">
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="K24">
         <f>VLOOKUP(J24,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <f>J24/2</f>
-        <v>12500</v>
-      </c>
-      <c r="M24" s="3">
+        <f t="shared" si="2"/>
+        <v>250</v>
+      </c>
+      <c r="M24">
         <f>VLOOKUP(L24,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="N24">
-        <f>F24/2+D24</f>
-        <v>12500</v>
-      </c>
-      <c r="O24" s="3">
+        <f t="shared" si="3"/>
+        <v>250</v>
+      </c>
+      <c r="O24">
         <f>VLOOKUP(N24,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
-      </c>
-      <c r="P24" s="2">
-        <f>F24+E24+D24</f>
-        <v>25300</v>
+        <v>3</v>
+      </c>
+      <c r="P24" s="1">
+        <f t="shared" si="4"/>
+        <v>800</v>
       </c>
       <c r="Q24">
         <f>VLOOKUP(P24,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <f>P24/2</f>
-        <v>12650</v>
-      </c>
-      <c r="S24" s="3">
+        <f t="shared" si="5"/>
+        <v>400</v>
+      </c>
+      <c r="S24">
         <f>VLOOKUP(R24,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="T24">
-        <f>F24/2+E24+D24</f>
-        <v>12800</v>
-      </c>
-      <c r="U24" s="3">
+        <f t="shared" si="6"/>
+        <v>550</v>
+      </c>
+      <c r="U24">
         <f>VLOOKUP(T24,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.2">
@@ -2991,7 +2990,7 @@
       <c r="B25">
         <v>3</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="2" t="s">
         <v>140</v>
       </c>
       <c r="D25">
@@ -3000,69 +2999,69 @@
       <c r="E25">
         <v>300</v>
       </c>
-      <c r="F25" s="2">
-        <f>VLOOKUP(Data!B68,LookupTables!$A$2:$C$11,3)</f>
-        <v>25000</v>
+      <c r="F25" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>500</v>
       </c>
       <c r="G25">
         <f>VLOOKUP(F25,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="H25">
-        <f>F25/2</f>
-        <v>12500</v>
-      </c>
-      <c r="I25" s="3">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="I25">
         <f>VLOOKUP(H25,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
-      </c>
-      <c r="J25" s="2">
-        <f>F25+D25</f>
-        <v>25000</v>
+        <v>3</v>
+      </c>
+      <c r="J25" s="1">
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="K25">
         <f>VLOOKUP(J25,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <f>J25/2</f>
-        <v>12500</v>
-      </c>
-      <c r="M25" s="3">
+        <f t="shared" si="2"/>
+        <v>250</v>
+      </c>
+      <c r="M25">
         <f>VLOOKUP(L25,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="N25">
-        <f>F25/2+D25</f>
-        <v>12500</v>
-      </c>
-      <c r="O25" s="3">
+        <f t="shared" si="3"/>
+        <v>250</v>
+      </c>
+      <c r="O25">
         <f>VLOOKUP(N25,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
-      </c>
-      <c r="P25" s="2">
-        <f>F25+E25+D25</f>
-        <v>25300</v>
+        <v>3</v>
+      </c>
+      <c r="P25" s="1">
+        <f t="shared" si="4"/>
+        <v>800</v>
       </c>
       <c r="Q25">
         <f>VLOOKUP(P25,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <f>P25/2</f>
-        <v>12650</v>
-      </c>
-      <c r="S25" s="3">
+        <f t="shared" si="5"/>
+        <v>400</v>
+      </c>
+      <c r="S25">
         <f>VLOOKUP(R25,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="T25">
-        <f>F25/2+E25+D25</f>
-        <v>12800</v>
-      </c>
-      <c r="U25" s="3">
+        <f t="shared" si="6"/>
+        <v>550</v>
+      </c>
+      <c r="U25">
         <f>VLOOKUP(T25,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.2">
@@ -3072,7 +3071,7 @@
       <c r="B26">
         <v>4</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D26">
@@ -3081,69 +3080,69 @@
       <c r="E26">
         <v>0</v>
       </c>
-      <c r="F26" s="2">
-        <f>VLOOKUP(Data!B18,LookupTables!$A$2:$C$11,3)</f>
-        <v>500</v>
+      <c r="F26" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>2500</v>
       </c>
       <c r="G26">
         <f>VLOOKUP(F26,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H26">
-        <f>F26/2</f>
-        <v>250</v>
-      </c>
-      <c r="I26" s="3">
+        <f t="shared" si="0"/>
+        <v>1250</v>
+      </c>
+      <c r="I26">
         <f>VLOOKUP(H26,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
-      </c>
-      <c r="J26" s="2">
-        <f>F26+D26</f>
-        <v>525</v>
+        <v>11</v>
+      </c>
+      <c r="J26" s="1">
+        <f t="shared" si="1"/>
+        <v>2525</v>
       </c>
       <c r="K26">
         <f>VLOOKUP(J26,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L26">
-        <f>J26/2</f>
-        <v>262.5</v>
-      </c>
-      <c r="M26" s="3">
+        <f t="shared" si="2"/>
+        <v>1262.5</v>
+      </c>
+      <c r="M26">
         <f>VLOOKUP(L26,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N26">
-        <f>F26/2+D26</f>
-        <v>275</v>
-      </c>
-      <c r="O26" s="3">
+        <f t="shared" si="3"/>
+        <v>1275</v>
+      </c>
+      <c r="O26">
         <f>VLOOKUP(N26,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
-      </c>
-      <c r="P26" s="2">
-        <f>F26+E26+D26</f>
-        <v>525</v>
+        <v>11</v>
+      </c>
+      <c r="P26" s="1">
+        <f t="shared" si="4"/>
+        <v>2525</v>
       </c>
       <c r="Q26">
         <f>VLOOKUP(P26,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="R26">
-        <f>P26/2</f>
-        <v>262.5</v>
-      </c>
-      <c r="S26" s="3">
+        <f t="shared" si="5"/>
+        <v>1262.5</v>
+      </c>
+      <c r="S26">
         <f>VLOOKUP(R26,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T26">
-        <f>F26/2+E26+D26</f>
-        <v>275</v>
-      </c>
-      <c r="U26" s="3">
+        <f t="shared" si="6"/>
+        <v>1275</v>
+      </c>
+      <c r="U26">
         <f>VLOOKUP(T26,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="38.25" x14ac:dyDescent="0.2">
@@ -3153,7 +3152,7 @@
       <c r="B27">
         <v>4</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="2" t="s">
         <v>112</v>
       </c>
       <c r="D27">
@@ -3162,67 +3161,67 @@
       <c r="E27">
         <v>5050</v>
       </c>
-      <c r="F27" s="2">
-        <f>VLOOKUP(Data!B38,LookupTables!$A$2:$C$11,3)</f>
-        <v>5000</v>
+      <c r="F27" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>2500</v>
       </c>
       <c r="G27">
         <f>VLOOKUP(F27,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H27">
-        <f>F27/2</f>
+        <f t="shared" si="0"/>
+        <v>1250</v>
+      </c>
+      <c r="I27">
+        <f>VLOOKUP(H27,LookupTables!$E$2:$F$18,2)</f>
+        <v>11</v>
+      </c>
+      <c r="J27" s="1">
+        <f t="shared" si="1"/>
         <v>2500</v>
-      </c>
-      <c r="I27" s="3">
-        <f>VLOOKUP(H27,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="J27" s="2">
-        <f>F27+D27</f>
-        <v>5000</v>
       </c>
       <c r="K27">
         <f>VLOOKUP(J27,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="L27">
-        <f>J27/2</f>
-        <v>2500</v>
-      </c>
-      <c r="M27" s="3">
+        <f t="shared" si="2"/>
+        <v>1250</v>
+      </c>
+      <c r="M27">
         <f>VLOOKUP(L27,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="N27">
-        <f>F27/2+D27</f>
-        <v>2500</v>
-      </c>
-      <c r="O27" s="3">
+        <f t="shared" si="3"/>
+        <v>1250</v>
+      </c>
+      <c r="O27">
         <f>VLOOKUP(N27,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="P27" s="2">
-        <f>F27+E27+D27</f>
-        <v>10050</v>
+        <v>11</v>
+      </c>
+      <c r="P27" s="1">
+        <f t="shared" si="4"/>
+        <v>7550</v>
       </c>
       <c r="Q27">
         <f>VLOOKUP(P27,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R27">
-        <f>P27/2</f>
-        <v>5025</v>
-      </c>
-      <c r="S27" s="3">
+        <f t="shared" si="5"/>
+        <v>3775</v>
+      </c>
+      <c r="S27">
         <f>VLOOKUP(R27,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="T27">
-        <f>F27/2+E27+D27</f>
-        <v>7550</v>
-      </c>
-      <c r="U27" s="3">
+        <f t="shared" si="6"/>
+        <v>6300</v>
+      </c>
+      <c r="U27">
         <f>VLOOKUP(T27,LookupTables!$E$2:$F$18,2)</f>
         <v>23</v>
       </c>
@@ -3234,7 +3233,7 @@
       <c r="B28">
         <v>4</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="2" t="s">
         <v>101</v>
       </c>
       <c r="D28">
@@ -3243,69 +3242,69 @@
       <c r="E28">
         <v>0</v>
       </c>
-      <c r="F28" s="2">
-        <f>VLOOKUP(Data!B59,LookupTables!$A$2:$C$11,3)</f>
-        <v>15000</v>
+      <c r="F28" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>2500</v>
       </c>
       <c r="G28">
         <f>VLOOKUP(F28,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H28">
-        <f>F28/2</f>
-        <v>7500</v>
-      </c>
-      <c r="I28" s="3">
+        <f t="shared" si="0"/>
+        <v>1250</v>
+      </c>
+      <c r="I28">
         <f>VLOOKUP(H28,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="J28" s="2">
-        <f>F28+D28</f>
-        <v>15100</v>
+        <v>11</v>
+      </c>
+      <c r="J28" s="1">
+        <f t="shared" si="1"/>
+        <v>2600</v>
       </c>
       <c r="K28">
         <f>VLOOKUP(J28,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="L28">
-        <f>J28/2</f>
-        <v>7550</v>
-      </c>
-      <c r="M28" s="3">
+        <f t="shared" si="2"/>
+        <v>1300</v>
+      </c>
+      <c r="M28">
         <f>VLOOKUP(L28,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="N28">
-        <f>F28/2+D28</f>
-        <v>7600</v>
-      </c>
-      <c r="O28" s="3">
+        <f t="shared" si="3"/>
+        <v>1350</v>
+      </c>
+      <c r="O28">
         <f>VLOOKUP(N28,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="P28" s="2">
-        <f>F28+E28+D28</f>
-        <v>15100</v>
+        <v>11</v>
+      </c>
+      <c r="P28" s="1">
+        <f t="shared" si="4"/>
+        <v>2600</v>
       </c>
       <c r="Q28">
         <f>VLOOKUP(P28,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="R28">
-        <f>P28/2</f>
-        <v>7550</v>
-      </c>
-      <c r="S28" s="3">
+        <f t="shared" si="5"/>
+        <v>1300</v>
+      </c>
+      <c r="S28">
         <f>VLOOKUP(R28,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="T28">
-        <f>F28/2+E28+D28</f>
-        <v>7600</v>
-      </c>
-      <c r="U28" s="3">
+        <f t="shared" si="6"/>
+        <v>1350</v>
+      </c>
+      <c r="U28">
         <f>VLOOKUP(T28,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
@@ -3315,7 +3314,7 @@
       <c r="B29">
         <v>4</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="2" t="s">
         <v>132</v>
       </c>
       <c r="D29">
@@ -3324,69 +3323,69 @@
       <c r="E29">
         <v>400</v>
       </c>
-      <c r="F29" s="2">
-        <f>VLOOKUP(Data!B60,LookupTables!$A$2:$C$11,3)</f>
-        <v>25000</v>
+      <c r="F29" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>2500</v>
       </c>
       <c r="G29">
         <f>VLOOKUP(F29,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="H29">
-        <f>F29/2</f>
-        <v>12500</v>
-      </c>
-      <c r="I29" s="3">
+        <f t="shared" si="0"/>
+        <v>1250</v>
+      </c>
+      <c r="I29">
         <f>VLOOKUP(H29,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
-      </c>
-      <c r="J29" s="2">
-        <f>F29+D29</f>
-        <v>25000</v>
+        <v>11</v>
+      </c>
+      <c r="J29" s="1">
+        <f t="shared" si="1"/>
+        <v>2500</v>
       </c>
       <c r="K29">
         <f>VLOOKUP(J29,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="L29">
-        <f>J29/2</f>
-        <v>12500</v>
-      </c>
-      <c r="M29" s="3">
+        <f t="shared" si="2"/>
+        <v>1250</v>
+      </c>
+      <c r="M29">
         <f>VLOOKUP(L29,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="N29">
-        <f>F29/2+D29</f>
-        <v>12500</v>
-      </c>
-      <c r="O29" s="3">
+        <f t="shared" si="3"/>
+        <v>1250</v>
+      </c>
+      <c r="O29">
         <f>VLOOKUP(N29,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
-      </c>
-      <c r="P29" s="2">
-        <f>F29+E29+D29</f>
-        <v>25400</v>
+        <v>11</v>
+      </c>
+      <c r="P29" s="1">
+        <f t="shared" si="4"/>
+        <v>2900</v>
       </c>
       <c r="Q29">
         <f>VLOOKUP(P29,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="R29">
-        <f>P29/2</f>
-        <v>12700</v>
-      </c>
-      <c r="S29" s="3">
+        <f t="shared" si="5"/>
+        <v>1450</v>
+      </c>
+      <c r="S29">
         <f>VLOOKUP(R29,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="T29">
-        <f>F29/2+E29+D29</f>
-        <v>12900</v>
-      </c>
-      <c r="U29" s="3">
+        <f t="shared" si="6"/>
+        <v>1650</v>
+      </c>
+      <c r="U29">
         <f>VLOOKUP(T29,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.2">
@@ -3396,7 +3395,7 @@
       <c r="B30">
         <v>4</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="2" t="s">
         <v>135</v>
       </c>
       <c r="D30">
@@ -3405,69 +3404,69 @@
       <c r="E30">
         <v>400</v>
       </c>
-      <c r="F30" s="2">
-        <f>VLOOKUP(Data!B63,LookupTables!$A$2:$C$11,3)</f>
-        <v>25000</v>
+      <c r="F30" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>2500</v>
       </c>
       <c r="G30">
         <f>VLOOKUP(F30,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="H30">
-        <f>F30/2</f>
-        <v>12500</v>
-      </c>
-      <c r="I30" s="3">
+        <f t="shared" si="0"/>
+        <v>1250</v>
+      </c>
+      <c r="I30">
         <f>VLOOKUP(H30,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
-      </c>
-      <c r="J30" s="2">
-        <f>F30+D30</f>
-        <v>25000</v>
+        <v>11</v>
+      </c>
+      <c r="J30" s="1">
+        <f t="shared" si="1"/>
+        <v>2500</v>
       </c>
       <c r="K30">
         <f>VLOOKUP(J30,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="L30">
-        <f>J30/2</f>
-        <v>12500</v>
-      </c>
-      <c r="M30" s="3">
+        <f t="shared" si="2"/>
+        <v>1250</v>
+      </c>
+      <c r="M30">
         <f>VLOOKUP(L30,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="N30">
-        <f>F30/2+D30</f>
-        <v>12500</v>
-      </c>
-      <c r="O30" s="3">
+        <f t="shared" si="3"/>
+        <v>1250</v>
+      </c>
+      <c r="O30">
         <f>VLOOKUP(N30,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
-      </c>
-      <c r="P30" s="2">
-        <f>F30+E30+D30</f>
-        <v>25400</v>
+        <v>11</v>
+      </c>
+      <c r="P30" s="1">
+        <f t="shared" si="4"/>
+        <v>2900</v>
       </c>
       <c r="Q30">
         <f>VLOOKUP(P30,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="R30">
-        <f>P30/2</f>
-        <v>12700</v>
-      </c>
-      <c r="S30" s="3">
+        <f t="shared" si="5"/>
+        <v>1450</v>
+      </c>
+      <c r="S30">
         <f>VLOOKUP(R30,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="T30">
-        <f>F30/2+E30+D30</f>
-        <v>12900</v>
-      </c>
-      <c r="U30" s="3">
+        <f t="shared" si="6"/>
+        <v>1650</v>
+      </c>
+      <c r="U30">
         <f>VLOOKUP(T30,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.2">
@@ -3477,7 +3476,7 @@
       <c r="B31">
         <v>4</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="2" t="s">
         <v>137</v>
       </c>
       <c r="D31">
@@ -3486,69 +3485,69 @@
       <c r="E31">
         <v>400</v>
       </c>
-      <c r="F31" s="2">
-        <f>VLOOKUP(Data!B65,LookupTables!$A$2:$C$11,3)</f>
-        <v>25000</v>
+      <c r="F31" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>2500</v>
       </c>
       <c r="G31">
         <f>VLOOKUP(F31,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="H31">
-        <f>F31/2</f>
-        <v>12500</v>
-      </c>
-      <c r="I31" s="3">
+        <f t="shared" si="0"/>
+        <v>1250</v>
+      </c>
+      <c r="I31">
         <f>VLOOKUP(H31,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
-      </c>
-      <c r="J31" s="2">
-        <f>F31+D31</f>
-        <v>25000</v>
+        <v>11</v>
+      </c>
+      <c r="J31" s="1">
+        <f t="shared" si="1"/>
+        <v>2500</v>
       </c>
       <c r="K31">
         <f>VLOOKUP(J31,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="L31">
-        <f>J31/2</f>
-        <v>12500</v>
-      </c>
-      <c r="M31" s="3">
+        <f t="shared" si="2"/>
+        <v>1250</v>
+      </c>
+      <c r="M31">
         <f>VLOOKUP(L31,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="N31">
-        <f>F31/2+D31</f>
-        <v>12500</v>
-      </c>
-      <c r="O31" s="3">
+        <f t="shared" si="3"/>
+        <v>1250</v>
+      </c>
+      <c r="O31">
         <f>VLOOKUP(N31,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
-      </c>
-      <c r="P31" s="2">
-        <f>F31+E31+D31</f>
-        <v>25400</v>
+        <v>11</v>
+      </c>
+      <c r="P31" s="1">
+        <f t="shared" si="4"/>
+        <v>2900</v>
       </c>
       <c r="Q31">
         <f>VLOOKUP(P31,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="R31">
-        <f>P31/2</f>
-        <v>12700</v>
-      </c>
-      <c r="S31" s="3">
+        <f t="shared" si="5"/>
+        <v>1450</v>
+      </c>
+      <c r="S31">
         <f>VLOOKUP(R31,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="T31">
-        <f>F31/2+E31+D31</f>
-        <v>12900</v>
-      </c>
-      <c r="U31" s="3">
+        <f t="shared" si="6"/>
+        <v>1650</v>
+      </c>
+      <c r="U31">
         <f>VLOOKUP(T31,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.2">
@@ -3558,7 +3557,7 @@
       <c r="B32">
         <v>5</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D32">
@@ -3567,69 +3566,69 @@
       <c r="E32">
         <v>50</v>
       </c>
-      <c r="F32" s="2">
-        <f>VLOOKUP(Data!B3,LookupTables!$A$2:$C$11,3)</f>
-        <v>25</v>
+      <c r="F32" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>5000</v>
       </c>
       <c r="G32">
         <f>VLOOKUP(F32,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H32">
-        <f>F32/2</f>
-        <v>12.5</v>
-      </c>
-      <c r="I32" s="3">
+        <f t="shared" si="0"/>
+        <v>2500</v>
+      </c>
+      <c r="I32">
         <f>VLOOKUP(H32,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="2">
-        <f>F32+D32</f>
-        <v>25</v>
+        <v>17</v>
+      </c>
+      <c r="J32" s="1">
+        <f t="shared" si="1"/>
+        <v>5000</v>
       </c>
       <c r="K32">
         <f>VLOOKUP(J32,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L32">
-        <f>J32/2</f>
-        <v>12.5</v>
-      </c>
-      <c r="M32" s="3">
+        <f t="shared" si="2"/>
+        <v>2500</v>
+      </c>
+      <c r="M32">
         <f>VLOOKUP(L32,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N32">
-        <f>F32/2+D32</f>
-        <v>12.5</v>
-      </c>
-      <c r="O32" s="3">
+        <f t="shared" si="3"/>
+        <v>2500</v>
+      </c>
+      <c r="O32">
         <f>VLOOKUP(N32,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
-      </c>
-      <c r="P32" s="2">
-        <f>F32+E32+D32</f>
-        <v>75</v>
+        <v>17</v>
+      </c>
+      <c r="P32" s="1">
+        <f t="shared" si="4"/>
+        <v>5050</v>
       </c>
       <c r="Q32">
         <f>VLOOKUP(P32,LookupTables!$E$2:$F$18,2)</f>
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="R32">
-        <f>P32/2</f>
-        <v>37.5</v>
-      </c>
-      <c r="S32" s="3">
+        <f t="shared" si="5"/>
+        <v>2525</v>
+      </c>
+      <c r="S32">
         <f>VLOOKUP(R32,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T32">
-        <f>F32/2+E32+D32</f>
-        <v>62.5</v>
-      </c>
-      <c r="U32" s="3">
+        <f t="shared" si="6"/>
+        <v>2550</v>
+      </c>
+      <c r="U32">
         <f>VLOOKUP(T32,LookupTables!$E$2:$F$18,2)</f>
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.2">
@@ -3639,7 +3638,7 @@
       <c r="B33">
         <v>5</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="2" t="s">
         <v>81</v>
       </c>
       <c r="D33">
@@ -3648,69 +3647,69 @@
       <c r="E33">
         <v>0</v>
       </c>
-      <c r="F33" s="2">
-        <f>VLOOKUP(Data!B7,LookupTables!$A$2:$C$11,3)</f>
-        <v>25</v>
+      <c r="F33" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>5000</v>
       </c>
       <c r="G33">
         <f>VLOOKUP(F33,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H33">
-        <f>F33/2</f>
-        <v>12.5</v>
-      </c>
-      <c r="I33" s="3">
+        <f t="shared" si="0"/>
+        <v>2500</v>
+      </c>
+      <c r="I33">
         <f>VLOOKUP(H33,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="2">
-        <f>F33+D33</f>
-        <v>1025</v>
+        <v>17</v>
+      </c>
+      <c r="J33" s="1">
+        <f t="shared" si="1"/>
+        <v>6000</v>
       </c>
       <c r="K33">
         <f>VLOOKUP(J33,LookupTables!$E$2:$F$18,2)</f>
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="L33">
-        <f>J33/2</f>
-        <v>512.5</v>
-      </c>
-      <c r="M33" s="3">
+        <f t="shared" si="2"/>
+        <v>3000</v>
+      </c>
+      <c r="M33">
         <f>VLOOKUP(L33,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="N33">
-        <f>F33/2+D33</f>
-        <v>1012.5</v>
-      </c>
-      <c r="O33" s="3">
+        <f t="shared" si="3"/>
+        <v>3500</v>
+      </c>
+      <c r="O33">
         <f>VLOOKUP(N33,LookupTables!$E$2:$F$18,2)</f>
-        <v>9</v>
-      </c>
-      <c r="P33" s="2">
-        <f>F33+E33+D33</f>
-        <v>1025</v>
+        <v>21</v>
+      </c>
+      <c r="P33" s="1">
+        <f t="shared" si="4"/>
+        <v>6000</v>
       </c>
       <c r="Q33">
         <f>VLOOKUP(P33,LookupTables!$E$2:$F$18,2)</f>
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="R33">
-        <f>P33/2</f>
-        <v>512.5</v>
-      </c>
-      <c r="S33" s="3">
+        <f t="shared" si="5"/>
+        <v>3000</v>
+      </c>
+      <c r="S33">
         <f>VLOOKUP(R33,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="T33">
-        <f>F33/2+E33+D33</f>
-        <v>1012.5</v>
-      </c>
-      <c r="U33" s="3">
+        <f t="shared" si="6"/>
+        <v>3500</v>
+      </c>
+      <c r="U33">
         <f>VLOOKUP(T33,LookupTables!$E$2:$F$18,2)</f>
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.2">
@@ -3720,7 +3719,7 @@
       <c r="B34">
         <v>5</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="2" t="s">
         <v>101</v>
       </c>
       <c r="D34">
@@ -3729,69 +3728,69 @@
       <c r="E34">
         <v>0</v>
       </c>
-      <c r="F34" s="2">
-        <f>VLOOKUP(Data!B27,LookupTables!$A$2:$C$11,3)</f>
-        <v>2500</v>
+      <c r="F34" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>5000</v>
       </c>
       <c r="G34">
         <f>VLOOKUP(F34,LookupTables!$E$2:$F$18,2)</f>
+        <v>23</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="0"/>
+        <v>2500</v>
+      </c>
+      <c r="I34">
+        <f>VLOOKUP(H34,LookupTables!$E$2:$F$18,2)</f>
         <v>17</v>
       </c>
-      <c r="H34">
-        <f>F34/2</f>
-        <v>1250</v>
-      </c>
-      <c r="I34" s="3">
-        <f>VLOOKUP(H34,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
-      </c>
-      <c r="J34" s="2">
-        <f>F34+D34</f>
-        <v>2600</v>
+      <c r="J34" s="1">
+        <f t="shared" si="1"/>
+        <v>5100</v>
       </c>
       <c r="K34">
         <f>VLOOKUP(J34,LookupTables!$E$2:$F$18,2)</f>
+        <v>23</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="2"/>
+        <v>2550</v>
+      </c>
+      <c r="M34">
+        <f>VLOOKUP(L34,LookupTables!$E$2:$F$18,2)</f>
         <v>17</v>
       </c>
-      <c r="L34">
-        <f>J34/2</f>
-        <v>1300</v>
-      </c>
-      <c r="M34" s="3">
-        <f>VLOOKUP(L34,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
-      </c>
       <c r="N34">
-        <f>F34/2+D34</f>
-        <v>1350</v>
-      </c>
-      <c r="O34" s="3">
+        <f t="shared" si="3"/>
+        <v>2600</v>
+      </c>
+      <c r="O34">
         <f>VLOOKUP(N34,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
-      </c>
-      <c r="P34" s="2">
-        <f>F34+E34+D34</f>
-        <v>2600</v>
+        <v>17</v>
+      </c>
+      <c r="P34" s="1">
+        <f t="shared" si="4"/>
+        <v>5100</v>
       </c>
       <c r="Q34">
         <f>VLOOKUP(P34,LookupTables!$E$2:$F$18,2)</f>
+        <v>23</v>
+      </c>
+      <c r="R34">
+        <f t="shared" si="5"/>
+        <v>2550</v>
+      </c>
+      <c r="S34">
+        <f>VLOOKUP(R34,LookupTables!$E$2:$F$18,2)</f>
         <v>17</v>
       </c>
-      <c r="R34">
-        <f>P34/2</f>
-        <v>1300</v>
-      </c>
-      <c r="S34" s="3">
-        <f>VLOOKUP(R34,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
-      </c>
       <c r="T34">
-        <f>F34/2+E34+D34</f>
-        <v>1350</v>
-      </c>
-      <c r="U34" s="3">
+        <f t="shared" si="6"/>
+        <v>2600</v>
+      </c>
+      <c r="U34">
         <f>VLOOKUP(T34,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.2">
@@ -3801,7 +3800,7 @@
       <c r="B35">
         <v>5</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="2" t="s">
         <v>103</v>
       </c>
       <c r="D35">
@@ -3810,69 +3809,69 @@
       <c r="E35">
         <v>0</v>
       </c>
-      <c r="F35" s="2">
-        <f>VLOOKUP(Data!B29,LookupTables!$A$2:$C$11,3)</f>
-        <v>2500</v>
+      <c r="F35" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>5000</v>
       </c>
       <c r="G35">
         <f>VLOOKUP(F35,LookupTables!$E$2:$F$18,2)</f>
+        <v>23</v>
+      </c>
+      <c r="H35">
+        <f t="shared" ref="H35:H66" si="7">F35/2</f>
+        <v>2500</v>
+      </c>
+      <c r="I35">
+        <f>VLOOKUP(H35,LookupTables!$E$2:$F$18,2)</f>
         <v>17</v>
       </c>
-      <c r="H35">
-        <f>F35/2</f>
-        <v>1250</v>
-      </c>
-      <c r="I35" s="3">
-        <f>VLOOKUP(H35,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
-      </c>
-      <c r="J35" s="2">
-        <f>F35+D35</f>
-        <v>3500</v>
+      <c r="J35" s="1">
+        <f t="shared" ref="J35:J66" si="8">F35+D35</f>
+        <v>6000</v>
       </c>
       <c r="K35">
         <f>VLOOKUP(J35,LookupTables!$E$2:$F$18,2)</f>
+        <v>23</v>
+      </c>
+      <c r="L35">
+        <f t="shared" ref="L35:L66" si="9">J35/2</f>
+        <v>3000</v>
+      </c>
+      <c r="M35">
+        <f>VLOOKUP(L35,LookupTables!$E$2:$F$18,2)</f>
+        <v>19</v>
+      </c>
+      <c r="N35">
+        <f t="shared" ref="N35:N66" si="10">F35/2+D35</f>
+        <v>3500</v>
+      </c>
+      <c r="O35">
+        <f>VLOOKUP(N35,LookupTables!$E$2:$F$18,2)</f>
         <v>21</v>
       </c>
-      <c r="L35">
-        <f>J35/2</f>
-        <v>1750</v>
-      </c>
-      <c r="M35" s="3">
-        <f>VLOOKUP(L35,LookupTables!$E$2:$F$18,2)</f>
-        <v>13</v>
-      </c>
-      <c r="N35">
-        <f>F35/2+D35</f>
-        <v>2250</v>
-      </c>
-      <c r="O35" s="3">
-        <f>VLOOKUP(N35,LookupTables!$E$2:$F$18,2)</f>
-        <v>15</v>
-      </c>
-      <c r="P35" s="2">
-        <f>F35+E35+D35</f>
-        <v>3500</v>
+      <c r="P35" s="1">
+        <f t="shared" ref="P35:P66" si="11">F35+E35+D35</f>
+        <v>6000</v>
       </c>
       <c r="Q35">
         <f>VLOOKUP(P35,LookupTables!$E$2:$F$18,2)</f>
+        <v>23</v>
+      </c>
+      <c r="R35">
+        <f t="shared" ref="R35:R66" si="12">P35/2</f>
+        <v>3000</v>
+      </c>
+      <c r="S35">
+        <f>VLOOKUP(R35,LookupTables!$E$2:$F$18,2)</f>
+        <v>19</v>
+      </c>
+      <c r="T35">
+        <f t="shared" ref="T35:T66" si="13">F35/2+E35+D35</f>
+        <v>3500</v>
+      </c>
+      <c r="U35">
+        <f>VLOOKUP(T35,LookupTables!$E$2:$F$18,2)</f>
         <v>21</v>
-      </c>
-      <c r="R35">
-        <f>P35/2</f>
-        <v>1750</v>
-      </c>
-      <c r="S35" s="3">
-        <f>VLOOKUP(R35,LookupTables!$E$2:$F$18,2)</f>
-        <v>13</v>
-      </c>
-      <c r="T35">
-        <f>F35/2+E35+D35</f>
-        <v>2250</v>
-      </c>
-      <c r="U35" s="3">
-        <f>VLOOKUP(T35,LookupTables!$E$2:$F$18,2)</f>
-        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
@@ -3882,7 +3881,7 @@
       <c r="B36">
         <v>5</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="2" t="s">
         <v>111</v>
       </c>
       <c r="D36">
@@ -3891,8 +3890,8 @@
       <c r="E36">
         <v>200</v>
       </c>
-      <c r="F36" s="2">
-        <f>VLOOKUP(Data!B37,LookupTables!$A$2:$C$11,3)</f>
+      <c r="F36" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
         <v>5000</v>
       </c>
       <c r="G36">
@@ -3900,15 +3899,15 @@
         <v>23</v>
       </c>
       <c r="H36">
-        <f>F36/2</f>
+        <f t="shared" si="7"/>
         <v>2500</v>
       </c>
-      <c r="I36" s="3">
+      <c r="I36">
         <f>VLOOKUP(H36,LookupTables!$E$2:$F$18,2)</f>
         <v>17</v>
       </c>
-      <c r="J36" s="2">
-        <f>F36+D36</f>
+      <c r="J36" s="1">
+        <f t="shared" si="8"/>
         <v>5250</v>
       </c>
       <c r="K36">
@@ -3916,23 +3915,23 @@
         <v>23</v>
       </c>
       <c r="L36">
-        <f>J36/2</f>
+        <f t="shared" si="9"/>
         <v>2625</v>
       </c>
-      <c r="M36" s="3">
+      <c r="M36">
         <f>VLOOKUP(L36,LookupTables!$E$2:$F$18,2)</f>
         <v>17</v>
       </c>
       <c r="N36">
-        <f>F36/2+D36</f>
+        <f t="shared" si="10"/>
         <v>2750</v>
       </c>
-      <c r="O36" s="3">
+      <c r="O36">
         <f>VLOOKUP(N36,LookupTables!$E$2:$F$18,2)</f>
         <v>17</v>
       </c>
-      <c r="P36" s="2">
-        <f>F36+E36+D36</f>
+      <c r="P36" s="1">
+        <f t="shared" si="11"/>
         <v>5450</v>
       </c>
       <c r="Q36">
@@ -3940,18 +3939,18 @@
         <v>23</v>
       </c>
       <c r="R36">
-        <f>P36/2</f>
+        <f t="shared" si="12"/>
         <v>2725</v>
       </c>
-      <c r="S36" s="3">
+      <c r="S36">
         <f>VLOOKUP(R36,LookupTables!$E$2:$F$18,2)</f>
         <v>17</v>
       </c>
       <c r="T36">
-        <f>F36/2+E36+D36</f>
+        <f t="shared" si="13"/>
         <v>2950</v>
       </c>
-      <c r="U36" s="3">
+      <c r="U36">
         <f>VLOOKUP(T36,LookupTables!$E$2:$F$18,2)</f>
         <v>17</v>
       </c>
@@ -3963,7 +3962,7 @@
       <c r="B37">
         <v>5</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="2" t="s">
         <v>119</v>
       </c>
       <c r="D37">
@@ -3972,8 +3971,8 @@
       <c r="E37">
         <v>0</v>
       </c>
-      <c r="F37" s="2">
-        <f>VLOOKUP(Data!B45,LookupTables!$A$2:$C$11,3)</f>
+      <c r="F37" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
         <v>5000</v>
       </c>
       <c r="G37">
@@ -3981,15 +3980,15 @@
         <v>23</v>
       </c>
       <c r="H37">
-        <f>F37/2</f>
+        <f t="shared" si="7"/>
         <v>2500</v>
       </c>
-      <c r="I37" s="3">
+      <c r="I37">
         <f>VLOOKUP(H37,LookupTables!$E$2:$F$18,2)</f>
         <v>17</v>
       </c>
-      <c r="J37" s="2">
-        <f>F37+D37</f>
+      <c r="J37" s="1">
+        <f t="shared" si="8"/>
         <v>6000</v>
       </c>
       <c r="K37">
@@ -3997,23 +3996,23 @@
         <v>23</v>
       </c>
       <c r="L37">
-        <f>J37/2</f>
+        <f t="shared" si="9"/>
         <v>3000</v>
       </c>
-      <c r="M37" s="3">
+      <c r="M37">
         <f>VLOOKUP(L37,LookupTables!$E$2:$F$18,2)</f>
         <v>19</v>
       </c>
       <c r="N37">
-        <f>F37/2+D37</f>
+        <f t="shared" si="10"/>
         <v>3500</v>
       </c>
-      <c r="O37" s="3">
+      <c r="O37">
         <f>VLOOKUP(N37,LookupTables!$E$2:$F$18,2)</f>
         <v>21</v>
       </c>
-      <c r="P37" s="2">
-        <f>F37+E37+D37</f>
+      <c r="P37" s="1">
+        <f t="shared" si="11"/>
         <v>6000</v>
       </c>
       <c r="Q37">
@@ -4021,18 +4020,18 @@
         <v>23</v>
       </c>
       <c r="R37">
-        <f>P37/2</f>
+        <f t="shared" si="12"/>
         <v>3000</v>
       </c>
-      <c r="S37" s="3">
+      <c r="S37">
         <f>VLOOKUP(R37,LookupTables!$E$2:$F$18,2)</f>
         <v>19</v>
       </c>
       <c r="T37">
-        <f>F37/2+E37+D37</f>
+        <f t="shared" si="13"/>
         <v>3500</v>
       </c>
-      <c r="U37" s="3">
+      <c r="U37">
         <f>VLOOKUP(T37,LookupTables!$E$2:$F$18,2)</f>
         <v>21</v>
       </c>
@@ -4044,7 +4043,7 @@
       <c r="B38">
         <v>5</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="2" t="s">
         <v>124</v>
       </c>
       <c r="D38">
@@ -4053,69 +4052,69 @@
       <c r="E38">
         <v>0</v>
       </c>
-      <c r="F38" s="2">
-        <f>VLOOKUP(Data!B50,LookupTables!$A$2:$C$11,3)</f>
-        <v>15000</v>
+      <c r="F38" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>5000</v>
       </c>
       <c r="G38">
         <f>VLOOKUP(F38,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H38">
-        <f>F38/2</f>
-        <v>7500</v>
-      </c>
-      <c r="I38" s="3">
+        <f t="shared" si="7"/>
+        <v>2500</v>
+      </c>
+      <c r="I38">
         <f>VLOOKUP(H38,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="J38" s="2">
-        <f>F38+D38</f>
-        <v>15500</v>
+        <v>17</v>
+      </c>
+      <c r="J38" s="1">
+        <f t="shared" si="8"/>
+        <v>5500</v>
       </c>
       <c r="K38">
         <f>VLOOKUP(J38,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L38">
-        <f>J38/2</f>
-        <v>7750</v>
-      </c>
-      <c r="M38" s="3">
+        <f t="shared" si="9"/>
+        <v>2750</v>
+      </c>
+      <c r="M38">
         <f>VLOOKUP(L38,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="N38">
-        <f>F38/2+D38</f>
-        <v>8000</v>
-      </c>
-      <c r="O38" s="3">
+        <f t="shared" si="10"/>
+        <v>3000</v>
+      </c>
+      <c r="O38">
         <f>VLOOKUP(N38,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
-      </c>
-      <c r="P38" s="2">
-        <f>F38+E38+D38</f>
-        <v>15500</v>
+        <v>19</v>
+      </c>
+      <c r="P38" s="1">
+        <f t="shared" si="11"/>
+        <v>5500</v>
       </c>
       <c r="Q38">
         <f>VLOOKUP(P38,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="R38">
-        <f>P38/2</f>
-        <v>7750</v>
-      </c>
-      <c r="S38" s="3">
+        <f t="shared" si="12"/>
+        <v>2750</v>
+      </c>
+      <c r="S38">
         <f>VLOOKUP(R38,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="T38">
-        <f>F38/2+E38+D38</f>
-        <v>8000</v>
-      </c>
-      <c r="U38" s="3">
+        <f t="shared" si="13"/>
+        <v>3000</v>
+      </c>
+      <c r="U38">
         <f>VLOOKUP(T38,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.2">
@@ -4125,7 +4124,7 @@
       <c r="B39">
         <v>5</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="2" t="s">
         <v>125</v>
       </c>
       <c r="D39">
@@ -4134,69 +4133,69 @@
       <c r="E39">
         <v>0</v>
       </c>
-      <c r="F39" s="2">
-        <f>VLOOKUP(Data!B51,LookupTables!$A$2:$C$11,3)</f>
-        <v>15000</v>
+      <c r="F39" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>5000</v>
       </c>
       <c r="G39">
         <f>VLOOKUP(F39,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H39">
-        <f>F39/2</f>
-        <v>7500</v>
-      </c>
-      <c r="I39" s="3">
+        <f t="shared" si="7"/>
+        <v>2500</v>
+      </c>
+      <c r="I39">
         <f>VLOOKUP(H39,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="J39" s="2">
-        <f>F39+D39</f>
-        <v>16000</v>
+        <v>17</v>
+      </c>
+      <c r="J39" s="1">
+        <f t="shared" si="8"/>
+        <v>6000</v>
       </c>
       <c r="K39">
         <f>VLOOKUP(J39,LookupTables!$E$2:$F$18,2)</f>
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L39">
-        <f>J39/2</f>
-        <v>8000</v>
-      </c>
-      <c r="M39" s="3">
+        <f t="shared" si="9"/>
+        <v>3000</v>
+      </c>
+      <c r="M39">
         <f>VLOOKUP(L39,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N39">
-        <f>F39/2+D39</f>
-        <v>8500</v>
-      </c>
-      <c r="O39" s="3">
+        <f t="shared" si="10"/>
+        <v>3500</v>
+      </c>
+      <c r="O39">
         <f>VLOOKUP(N39,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
-      </c>
-      <c r="P39" s="2">
-        <f>F39+E39+D39</f>
-        <v>16000</v>
+        <v>21</v>
+      </c>
+      <c r="P39" s="1">
+        <f t="shared" si="11"/>
+        <v>6000</v>
       </c>
       <c r="Q39">
         <f>VLOOKUP(P39,LookupTables!$E$2:$F$18,2)</f>
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R39">
-        <f>P39/2</f>
-        <v>8000</v>
-      </c>
-      <c r="S39" s="3">
+        <f t="shared" si="12"/>
+        <v>3000</v>
+      </c>
+      <c r="S39">
         <f>VLOOKUP(R39,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="T39">
-        <f>F39/2+E39+D39</f>
-        <v>8500</v>
-      </c>
-      <c r="U39" s="3">
+        <f t="shared" si="13"/>
+        <v>3500</v>
+      </c>
+      <c r="U39">
         <f>VLOOKUP(T39,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
@@ -4206,7 +4205,7 @@
       <c r="B40">
         <v>5</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="2" t="s">
         <v>128</v>
       </c>
       <c r="D40">
@@ -4215,69 +4214,69 @@
       <c r="E40">
         <v>1000</v>
       </c>
-      <c r="F40" s="2">
-        <f>VLOOKUP(Data!B54,LookupTables!$A$2:$C$11,3)</f>
-        <v>15000</v>
+      <c r="F40" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>5000</v>
       </c>
       <c r="G40">
         <f>VLOOKUP(F40,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H40">
-        <f>F40/2</f>
-        <v>7500</v>
-      </c>
-      <c r="I40" s="3">
+        <f t="shared" si="7"/>
+        <v>2500</v>
+      </c>
+      <c r="I40">
         <f>VLOOKUP(H40,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="J40" s="2">
-        <f>F40+D40</f>
-        <v>15000</v>
+        <v>17</v>
+      </c>
+      <c r="J40" s="1">
+        <f t="shared" si="8"/>
+        <v>5000</v>
       </c>
       <c r="K40">
         <f>VLOOKUP(J40,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L40">
-        <f>J40/2</f>
-        <v>7500</v>
-      </c>
-      <c r="M40" s="3">
+        <f t="shared" si="9"/>
+        <v>2500</v>
+      </c>
+      <c r="M40">
         <f>VLOOKUP(L40,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="N40">
-        <f>F40/2+D40</f>
-        <v>7500</v>
-      </c>
-      <c r="O40" s="3">
+        <f t="shared" si="10"/>
+        <v>2500</v>
+      </c>
+      <c r="O40">
         <f>VLOOKUP(N40,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="P40" s="2">
-        <f>F40+E40+D40</f>
-        <v>16000</v>
+        <v>17</v>
+      </c>
+      <c r="P40" s="1">
+        <f t="shared" si="11"/>
+        <v>6000</v>
       </c>
       <c r="Q40">
         <f>VLOOKUP(P40,LookupTables!$E$2:$F$18,2)</f>
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R40">
-        <f>P40/2</f>
-        <v>8000</v>
-      </c>
-      <c r="S40" s="3">
+        <f t="shared" si="12"/>
+        <v>3000</v>
+      </c>
+      <c r="S40">
         <f>VLOOKUP(R40,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="T40">
-        <f>F40/2+E40+D40</f>
-        <v>8500</v>
-      </c>
-      <c r="U40" s="3">
+        <f t="shared" si="13"/>
+        <v>3500</v>
+      </c>
+      <c r="U40">
         <f>VLOOKUP(T40,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.2">
@@ -4287,7 +4286,7 @@
       <c r="B41">
         <v>5</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="2" t="s">
         <v>107</v>
       </c>
       <c r="D41">
@@ -4296,69 +4295,69 @@
       <c r="E41">
         <v>100</v>
       </c>
-      <c r="F41" s="2">
-        <f>VLOOKUP(Data!B58,LookupTables!$A$2:$C$11,3)</f>
-        <v>15000</v>
+      <c r="F41" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>5000</v>
       </c>
       <c r="G41">
         <f>VLOOKUP(F41,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H41">
-        <f>F41/2</f>
-        <v>7500</v>
-      </c>
-      <c r="I41" s="3">
+        <f t="shared" si="7"/>
+        <v>2500</v>
+      </c>
+      <c r="I41">
         <f>VLOOKUP(H41,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="J41" s="2">
-        <f>F41+D41</f>
-        <v>15000</v>
+        <v>17</v>
+      </c>
+      <c r="J41" s="1">
+        <f t="shared" si="8"/>
+        <v>5000</v>
       </c>
       <c r="K41">
         <f>VLOOKUP(J41,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L41">
-        <f>J41/2</f>
-        <v>7500</v>
-      </c>
-      <c r="M41" s="3">
+        <f t="shared" si="9"/>
+        <v>2500</v>
+      </c>
+      <c r="M41">
         <f>VLOOKUP(L41,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="N41">
-        <f>F41/2+D41</f>
-        <v>7500</v>
-      </c>
-      <c r="O41" s="3">
+        <f t="shared" si="10"/>
+        <v>2500</v>
+      </c>
+      <c r="O41">
         <f>VLOOKUP(N41,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="P41" s="2">
-        <f>F41+E41+D41</f>
-        <v>15100</v>
+        <v>17</v>
+      </c>
+      <c r="P41" s="1">
+        <f t="shared" si="11"/>
+        <v>5100</v>
       </c>
       <c r="Q41">
         <f>VLOOKUP(P41,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="R41">
-        <f>P41/2</f>
-        <v>7550</v>
-      </c>
-      <c r="S41" s="3">
+        <f t="shared" si="12"/>
+        <v>2550</v>
+      </c>
+      <c r="S41">
         <f>VLOOKUP(R41,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="T41">
-        <f>F41/2+E41+D41</f>
-        <v>7600</v>
-      </c>
-      <c r="U41" s="3">
+        <f t="shared" si="13"/>
+        <v>2600</v>
+      </c>
+      <c r="U41">
         <f>VLOOKUP(T41,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.2">
@@ -4368,7 +4367,7 @@
       <c r="B42">
         <v>5</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="2" t="s">
         <v>134</v>
       </c>
       <c r="D42">
@@ -4377,69 +4376,69 @@
       <c r="E42">
         <v>500</v>
       </c>
-      <c r="F42" s="2">
-        <f>VLOOKUP(Data!B62,LookupTables!$A$2:$C$11,3)</f>
-        <v>25000</v>
+      <c r="F42" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>5000</v>
       </c>
       <c r="G42">
         <f>VLOOKUP(F42,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H42">
-        <f>F42/2</f>
-        <v>12500</v>
-      </c>
-      <c r="I42" s="3">
+        <f t="shared" si="7"/>
+        <v>2500</v>
+      </c>
+      <c r="I42">
         <f>VLOOKUP(H42,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
-      </c>
-      <c r="J42" s="2">
-        <f>F42+D42</f>
-        <v>25000</v>
+        <v>17</v>
+      </c>
+      <c r="J42" s="1">
+        <f t="shared" si="8"/>
+        <v>5000</v>
       </c>
       <c r="K42">
         <f>VLOOKUP(J42,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L42">
-        <f>J42/2</f>
-        <v>12500</v>
-      </c>
-      <c r="M42" s="3">
+        <f t="shared" si="9"/>
+        <v>2500</v>
+      </c>
+      <c r="M42">
         <f>VLOOKUP(L42,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="N42">
-        <f>F42/2+D42</f>
-        <v>12500</v>
-      </c>
-      <c r="O42" s="3">
+        <f t="shared" si="10"/>
+        <v>2500</v>
+      </c>
+      <c r="O42">
         <f>VLOOKUP(N42,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
-      </c>
-      <c r="P42" s="2">
-        <f>F42+E42+D42</f>
-        <v>25500</v>
+        <v>17</v>
+      </c>
+      <c r="P42" s="1">
+        <f t="shared" si="11"/>
+        <v>5500</v>
       </c>
       <c r="Q42">
         <f>VLOOKUP(P42,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="R42">
-        <f>P42/2</f>
-        <v>12750</v>
-      </c>
-      <c r="S42" s="3">
+        <f t="shared" si="12"/>
+        <v>2750</v>
+      </c>
+      <c r="S42">
         <f>VLOOKUP(R42,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="T42">
-        <f>F42/2+E42+D42</f>
-        <v>13000</v>
-      </c>
-      <c r="U42" s="3">
+        <f t="shared" si="13"/>
+        <v>3000</v>
+      </c>
+      <c r="U42">
         <f>VLOOKUP(T42,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.2">
@@ -4449,7 +4448,7 @@
       <c r="B43">
         <v>5</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="2" t="s">
         <v>136</v>
       </c>
       <c r="D43">
@@ -4458,69 +4457,69 @@
       <c r="E43">
         <v>500</v>
       </c>
-      <c r="F43" s="2">
-        <f>VLOOKUP(Data!B64,LookupTables!$A$2:$C$11,3)</f>
-        <v>25000</v>
+      <c r="F43" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>5000</v>
       </c>
       <c r="G43">
         <f>VLOOKUP(F43,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H43">
-        <f>F43/2</f>
-        <v>12500</v>
-      </c>
-      <c r="I43" s="3">
+        <f t="shared" si="7"/>
+        <v>2500</v>
+      </c>
+      <c r="I43">
         <f>VLOOKUP(H43,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
-      </c>
-      <c r="J43" s="2">
-        <f>F43+D43</f>
-        <v>25000</v>
+        <v>17</v>
+      </c>
+      <c r="J43" s="1">
+        <f t="shared" si="8"/>
+        <v>5000</v>
       </c>
       <c r="K43">
         <f>VLOOKUP(J43,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L43">
-        <f>J43/2</f>
-        <v>12500</v>
-      </c>
-      <c r="M43" s="3">
+        <f t="shared" si="9"/>
+        <v>2500</v>
+      </c>
+      <c r="M43">
         <f>VLOOKUP(L43,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="N43">
-        <f>F43/2+D43</f>
-        <v>12500</v>
-      </c>
-      <c r="O43" s="3">
+        <f t="shared" si="10"/>
+        <v>2500</v>
+      </c>
+      <c r="O43">
         <f>VLOOKUP(N43,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
-      </c>
-      <c r="P43" s="2">
-        <f>F43+E43+D43</f>
-        <v>25500</v>
+        <v>17</v>
+      </c>
+      <c r="P43" s="1">
+        <f t="shared" si="11"/>
+        <v>5500</v>
       </c>
       <c r="Q43">
         <f>VLOOKUP(P43,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="R43">
-        <f>P43/2</f>
-        <v>12750</v>
-      </c>
-      <c r="S43" s="3">
+        <f t="shared" si="12"/>
+        <v>2750</v>
+      </c>
+      <c r="S43">
         <f>VLOOKUP(R43,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="T43">
-        <f>F43/2+E43+D43</f>
-        <v>13000</v>
-      </c>
-      <c r="U43" s="3">
+        <f t="shared" si="13"/>
+        <v>3000</v>
+      </c>
+      <c r="U43">
         <f>VLOOKUP(T43,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.2">
@@ -4530,7 +4529,7 @@
       <c r="B44">
         <v>5</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="2" t="s">
         <v>141</v>
       </c>
       <c r="D44">
@@ -4539,69 +4538,69 @@
       <c r="E44">
         <v>1</v>
       </c>
-      <c r="F44" s="2">
-        <f>VLOOKUP(Data!B69,LookupTables!$A$2:$C$11,3)</f>
-        <v>50000</v>
+      <c r="F44" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>5000</v>
       </c>
       <c r="G44">
         <f>VLOOKUP(F44,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H44">
-        <f>F44/2</f>
-        <v>25000</v>
-      </c>
-      <c r="I44" s="3">
+        <f t="shared" si="7"/>
+        <v>2500</v>
+      </c>
+      <c r="I44">
         <f>VLOOKUP(H44,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
-      </c>
-      <c r="J44" s="2">
-        <f>F44+D44</f>
-        <v>50000</v>
+        <v>17</v>
+      </c>
+      <c r="J44" s="1">
+        <f t="shared" si="8"/>
+        <v>5000</v>
       </c>
       <c r="K44">
         <f>VLOOKUP(J44,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L44">
-        <f>J44/2</f>
-        <v>25000</v>
-      </c>
-      <c r="M44" s="3">
+        <f t="shared" si="9"/>
+        <v>2500</v>
+      </c>
+      <c r="M44">
         <f>VLOOKUP(L44,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="N44">
-        <f>F44/2+D44</f>
-        <v>25000</v>
-      </c>
-      <c r="O44" s="3">
+        <f t="shared" si="10"/>
+        <v>2500</v>
+      </c>
+      <c r="O44">
         <f>VLOOKUP(N44,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
-      </c>
-      <c r="P44" s="2">
-        <f>F44+E44+D44</f>
-        <v>50001</v>
+        <v>17</v>
+      </c>
+      <c r="P44" s="1">
+        <f t="shared" si="11"/>
+        <v>5001</v>
       </c>
       <c r="Q44">
         <f>VLOOKUP(P44,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="R44">
-        <f>P44/2</f>
-        <v>25000.5</v>
-      </c>
-      <c r="S44" s="3">
+        <f t="shared" si="12"/>
+        <v>2500.5</v>
+      </c>
+      <c r="S44">
         <f>VLOOKUP(R44,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="T44">
-        <f>F44/2+E44+D44</f>
-        <v>25001</v>
-      </c>
-      <c r="U44" s="3">
+        <f t="shared" si="13"/>
+        <v>2501</v>
+      </c>
+      <c r="U44">
         <f>VLOOKUP(T44,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.2">
@@ -4611,7 +4610,7 @@
       <c r="B45">
         <v>5</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="2" t="s">
         <v>144</v>
       </c>
       <c r="D45">
@@ -4620,69 +4619,69 @@
       <c r="E45">
         <v>0</v>
       </c>
-      <c r="F45" s="2">
-        <f>VLOOKUP(Data!B72,LookupTables!$A$2:$C$11,3)</f>
-        <v>250000</v>
+      <c r="F45" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>5000</v>
       </c>
       <c r="G45">
         <f>VLOOKUP(F45,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H45">
-        <f>F45/2</f>
-        <v>125000</v>
-      </c>
-      <c r="I45" s="3">
+        <f t="shared" si="7"/>
+        <v>2500</v>
+      </c>
+      <c r="I45">
         <f>VLOOKUP(H45,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
-      </c>
-      <c r="J45" s="2">
-        <f>F45+D45</f>
-        <v>250050</v>
+        <v>17</v>
+      </c>
+      <c r="J45" s="1">
+        <f t="shared" si="8"/>
+        <v>5050</v>
       </c>
       <c r="K45">
         <f>VLOOKUP(J45,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L45">
-        <f>J45/2</f>
-        <v>125025</v>
-      </c>
-      <c r="M45" s="3">
+        <f t="shared" si="9"/>
+        <v>2525</v>
+      </c>
+      <c r="M45">
         <f>VLOOKUP(L45,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="N45">
-        <f>F45/2+D45</f>
-        <v>125050</v>
-      </c>
-      <c r="O45" s="3">
+        <f t="shared" si="10"/>
+        <v>2550</v>
+      </c>
+      <c r="O45">
         <f>VLOOKUP(N45,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
-      </c>
-      <c r="P45" s="2">
-        <f>F45+E45+D45</f>
-        <v>250050</v>
+        <v>17</v>
+      </c>
+      <c r="P45" s="1">
+        <f t="shared" si="11"/>
+        <v>5050</v>
       </c>
       <c r="Q45">
         <f>VLOOKUP(P45,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="R45">
-        <f>P45/2</f>
-        <v>125025</v>
-      </c>
-      <c r="S45" s="3">
+        <f t="shared" si="12"/>
+        <v>2525</v>
+      </c>
+      <c r="S45">
         <f>VLOOKUP(R45,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="T45">
-        <f>F45/2+E45+D45</f>
-        <v>125050</v>
-      </c>
-      <c r="U45" s="3">
+        <f t="shared" si="13"/>
+        <v>2550</v>
+      </c>
+      <c r="U45">
         <f>VLOOKUP(T45,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.2">
@@ -4692,7 +4691,7 @@
       <c r="B46">
         <v>6</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D46">
@@ -4701,69 +4700,69 @@
       <c r="E46">
         <v>500</v>
       </c>
-      <c r="F46" s="2">
-        <f>VLOOKUP(Data!B10,LookupTables!$A$2:$C$11,3)</f>
-        <v>250</v>
+      <c r="F46" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>15000</v>
       </c>
       <c r="G46">
         <f>VLOOKUP(F46,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="H46">
-        <f>F46/2</f>
-        <v>125</v>
-      </c>
-      <c r="I46" s="3">
+        <f t="shared" si="7"/>
+        <v>7500</v>
+      </c>
+      <c r="I46">
         <f>VLOOKUP(H46,LookupTables!$E$2:$F$18,2)</f>
-        <v>1</v>
-      </c>
-      <c r="J46" s="2">
-        <f>F46+D46</f>
-        <v>250</v>
+        <v>23</v>
+      </c>
+      <c r="J46" s="1">
+        <f t="shared" si="8"/>
+        <v>15000</v>
       </c>
       <c r="K46">
         <f>VLOOKUP(J46,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="L46">
-        <f>J46/2</f>
-        <v>125</v>
-      </c>
-      <c r="M46" s="3">
+        <f t="shared" si="9"/>
+        <v>7500</v>
+      </c>
+      <c r="M46">
         <f>VLOOKUP(L46,LookupTables!$E$2:$F$18,2)</f>
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="N46">
-        <f>F46/2+D46</f>
-        <v>125</v>
-      </c>
-      <c r="O46" s="3">
+        <f t="shared" si="10"/>
+        <v>7500</v>
+      </c>
+      <c r="O46">
         <f>VLOOKUP(N46,LookupTables!$E$2:$F$18,2)</f>
-        <v>1</v>
-      </c>
-      <c r="P46" s="2">
-        <f>F46+E46+D46</f>
-        <v>750</v>
+        <v>23</v>
+      </c>
+      <c r="P46" s="1">
+        <f t="shared" si="11"/>
+        <v>15500</v>
       </c>
       <c r="Q46">
         <f>VLOOKUP(P46,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="R46">
-        <f>P46/2</f>
-        <v>375</v>
-      </c>
-      <c r="S46" s="3">
+        <f t="shared" si="12"/>
+        <v>7750</v>
+      </c>
+      <c r="S46">
         <f>VLOOKUP(R46,LookupTables!$E$2:$F$18,2)</f>
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="T46">
-        <f>F46/2+E46+D46</f>
-        <v>625</v>
-      </c>
-      <c r="U46" s="3">
+        <f t="shared" si="13"/>
+        <v>8000</v>
+      </c>
+      <c r="U46">
         <f>VLOOKUP(T46,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.2">
@@ -4773,7 +4772,7 @@
       <c r="B47">
         <v>6</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="2" t="s">
         <v>87</v>
       </c>
       <c r="D47">
@@ -4782,69 +4781,69 @@
       <c r="E47">
         <v>1500</v>
       </c>
-      <c r="F47" s="2">
-        <f>VLOOKUP(Data!B13,LookupTables!$A$2:$C$11,3)</f>
-        <v>250</v>
+      <c r="F47" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>15000</v>
       </c>
       <c r="G47">
         <f>VLOOKUP(F47,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="H47">
-        <f>F47/2</f>
-        <v>125</v>
-      </c>
-      <c r="I47" s="3">
+        <f t="shared" si="7"/>
+        <v>7500</v>
+      </c>
+      <c r="I47">
         <f>VLOOKUP(H47,LookupTables!$E$2:$F$18,2)</f>
-        <v>1</v>
-      </c>
-      <c r="J47" s="2">
-        <f>F47+D47</f>
-        <v>250</v>
+        <v>23</v>
+      </c>
+      <c r="J47" s="1">
+        <f t="shared" si="8"/>
+        <v>15000</v>
       </c>
       <c r="K47">
         <f>VLOOKUP(J47,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="L47">
-        <f>J47/2</f>
-        <v>125</v>
-      </c>
-      <c r="M47" s="3">
+        <f t="shared" si="9"/>
+        <v>7500</v>
+      </c>
+      <c r="M47">
         <f>VLOOKUP(L47,LookupTables!$E$2:$F$18,2)</f>
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="N47">
-        <f>F47/2+D47</f>
-        <v>125</v>
-      </c>
-      <c r="O47" s="3">
+        <f t="shared" si="10"/>
+        <v>7500</v>
+      </c>
+      <c r="O47">
         <f>VLOOKUP(N47,LookupTables!$E$2:$F$18,2)</f>
-        <v>1</v>
-      </c>
-      <c r="P47" s="2">
-        <f>F47+E47+D47</f>
-        <v>1750</v>
+        <v>23</v>
+      </c>
+      <c r="P47" s="1">
+        <f t="shared" si="11"/>
+        <v>16500</v>
       </c>
       <c r="Q47">
         <f>VLOOKUP(P47,LookupTables!$E$2:$F$18,2)</f>
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="R47">
-        <f>P47/2</f>
-        <v>875</v>
-      </c>
-      <c r="S47" s="3">
+        <f t="shared" si="12"/>
+        <v>8250</v>
+      </c>
+      <c r="S47">
         <f>VLOOKUP(R47,LookupTables!$E$2:$F$18,2)</f>
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T47">
-        <f>F47/2+E47+D47</f>
-        <v>1625</v>
-      </c>
-      <c r="U47" s="3">
+        <f t="shared" si="13"/>
+        <v>9000</v>
+      </c>
+      <c r="U47">
         <f>VLOOKUP(T47,LookupTables!$E$2:$F$18,2)</f>
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.2">
@@ -4854,7 +4853,7 @@
       <c r="B48">
         <v>6</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D48">
@@ -4863,69 +4862,69 @@
       <c r="E48">
         <v>150</v>
       </c>
-      <c r="F48" s="2">
-        <f>VLOOKUP(Data!B15,LookupTables!$A$2:$C$11,3)</f>
-        <v>250</v>
+      <c r="F48" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>15000</v>
       </c>
       <c r="G48">
         <f>VLOOKUP(F48,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="H48">
-        <f>F48/2</f>
-        <v>125</v>
-      </c>
-      <c r="I48" s="3">
+        <f t="shared" si="7"/>
+        <v>7500</v>
+      </c>
+      <c r="I48">
         <f>VLOOKUP(H48,LookupTables!$E$2:$F$18,2)</f>
-        <v>1</v>
-      </c>
-      <c r="J48" s="2">
-        <f>F48+D48</f>
-        <v>250</v>
+        <v>23</v>
+      </c>
+      <c r="J48" s="1">
+        <f t="shared" si="8"/>
+        <v>15000</v>
       </c>
       <c r="K48">
         <f>VLOOKUP(J48,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="L48">
-        <f>J48/2</f>
-        <v>125</v>
-      </c>
-      <c r="M48" s="3">
+        <f t="shared" si="9"/>
+        <v>7500</v>
+      </c>
+      <c r="M48">
         <f>VLOOKUP(L48,LookupTables!$E$2:$F$18,2)</f>
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="N48">
-        <f>F48/2+D48</f>
-        <v>125</v>
-      </c>
-      <c r="O48" s="3">
+        <f t="shared" si="10"/>
+        <v>7500</v>
+      </c>
+      <c r="O48">
         <f>VLOOKUP(N48,LookupTables!$E$2:$F$18,2)</f>
-        <v>1</v>
-      </c>
-      <c r="P48" s="2">
-        <f>F48+E48+D48</f>
-        <v>400</v>
+        <v>23</v>
+      </c>
+      <c r="P48" s="1">
+        <f t="shared" si="11"/>
+        <v>15150</v>
       </c>
       <c r="Q48">
         <f>VLOOKUP(P48,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="R48">
-        <f>P48/2</f>
-        <v>200</v>
-      </c>
-      <c r="S48" s="3">
+        <f t="shared" si="12"/>
+        <v>7575</v>
+      </c>
+      <c r="S48">
         <f>VLOOKUP(R48,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="T48">
-        <f>F48/2+E48+D48</f>
-        <v>275</v>
-      </c>
-      <c r="U48" s="3">
+        <f t="shared" si="13"/>
+        <v>7650</v>
+      </c>
+      <c r="U48">
         <f>VLOOKUP(T48,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.2">
@@ -4935,7 +4934,7 @@
       <c r="B49">
         <v>6</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D49">
@@ -4944,69 +4943,69 @@
       <c r="E49">
         <v>1000</v>
       </c>
-      <c r="F49" s="2">
-        <f>VLOOKUP(Data!B19,LookupTables!$A$2:$C$11,3)</f>
-        <v>500</v>
+      <c r="F49" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>15000</v>
       </c>
       <c r="G49">
         <f>VLOOKUP(F49,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H49">
-        <f>F49/2</f>
-        <v>250</v>
-      </c>
-      <c r="I49" s="3">
+        <f t="shared" si="7"/>
+        <v>7500</v>
+      </c>
+      <c r="I49">
         <f>VLOOKUP(H49,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
-      </c>
-      <c r="J49" s="2">
-        <f>F49+D49</f>
-        <v>500</v>
+        <v>23</v>
+      </c>
+      <c r="J49" s="1">
+        <f t="shared" si="8"/>
+        <v>15000</v>
       </c>
       <c r="K49">
         <f>VLOOKUP(J49,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="L49">
-        <f>J49/2</f>
-        <v>250</v>
-      </c>
-      <c r="M49" s="3">
+        <f t="shared" si="9"/>
+        <v>7500</v>
+      </c>
+      <c r="M49">
         <f>VLOOKUP(L49,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="N49">
-        <f>F49/2+D49</f>
-        <v>250</v>
-      </c>
-      <c r="O49" s="3">
+        <f t="shared" si="10"/>
+        <v>7500</v>
+      </c>
+      <c r="O49">
         <f>VLOOKUP(N49,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
-      </c>
-      <c r="P49" s="2">
-        <f>F49+E49+D49</f>
-        <v>1500</v>
+        <v>23</v>
+      </c>
+      <c r="P49" s="1">
+        <f t="shared" si="11"/>
+        <v>16000</v>
       </c>
       <c r="Q49">
         <f>VLOOKUP(P49,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="R49">
-        <f>P49/2</f>
-        <v>750</v>
-      </c>
-      <c r="S49" s="3">
+        <f t="shared" si="12"/>
+        <v>8000</v>
+      </c>
+      <c r="S49">
         <f>VLOOKUP(R49,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T49">
-        <f>F49/2+E49+D49</f>
-        <v>1250</v>
-      </c>
-      <c r="U49" s="3">
+        <f t="shared" si="13"/>
+        <v>8500</v>
+      </c>
+      <c r="U49">
         <f>VLOOKUP(T49,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.2">
@@ -5016,7 +5015,7 @@
       <c r="B50">
         <v>6</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="2" t="s">
         <v>94</v>
       </c>
       <c r="D50">
@@ -5025,69 +5024,69 @@
       <c r="E50">
         <v>1000</v>
       </c>
-      <c r="F50" s="2">
-        <f>VLOOKUP(Data!B20,LookupTables!$A$2:$C$11,3)</f>
-        <v>500</v>
+      <c r="F50" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>15000</v>
       </c>
       <c r="G50">
         <f>VLOOKUP(F50,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H50">
-        <f>F50/2</f>
-        <v>250</v>
-      </c>
-      <c r="I50" s="3">
+        <f t="shared" si="7"/>
+        <v>7500</v>
+      </c>
+      <c r="I50">
         <f>VLOOKUP(H50,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
-      </c>
-      <c r="J50" s="2">
-        <f>F50+D50</f>
-        <v>500</v>
+        <v>23</v>
+      </c>
+      <c r="J50" s="1">
+        <f t="shared" si="8"/>
+        <v>15000</v>
       </c>
       <c r="K50">
         <f>VLOOKUP(J50,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="L50">
-        <f>J50/2</f>
-        <v>250</v>
-      </c>
-      <c r="M50" s="3">
+        <f t="shared" si="9"/>
+        <v>7500</v>
+      </c>
+      <c r="M50">
         <f>VLOOKUP(L50,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="N50">
-        <f>F50/2+D50</f>
-        <v>250</v>
-      </c>
-      <c r="O50" s="3">
+        <f t="shared" si="10"/>
+        <v>7500</v>
+      </c>
+      <c r="O50">
         <f>VLOOKUP(N50,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
-      </c>
-      <c r="P50" s="2">
-        <f>F50+E50+D50</f>
-        <v>1500</v>
+        <v>23</v>
+      </c>
+      <c r="P50" s="1">
+        <f t="shared" si="11"/>
+        <v>16000</v>
       </c>
       <c r="Q50">
         <f>VLOOKUP(P50,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="R50">
-        <f>P50/2</f>
-        <v>750</v>
-      </c>
-      <c r="S50" s="3">
+        <f t="shared" si="12"/>
+        <v>8000</v>
+      </c>
+      <c r="S50">
         <f>VLOOKUP(R50,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T50">
-        <f>F50/2+E50+D50</f>
-        <v>1250</v>
-      </c>
-      <c r="U50" s="3">
+        <f t="shared" si="13"/>
+        <v>8500</v>
+      </c>
+      <c r="U50">
         <f>VLOOKUP(T50,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.2">
@@ -5097,7 +5096,7 @@
       <c r="B51">
         <v>6</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="2" t="s">
         <v>96</v>
       </c>
       <c r="D51">
@@ -5106,69 +5105,69 @@
       <c r="E51">
         <v>100</v>
       </c>
-      <c r="F51" s="2">
-        <f>VLOOKUP(Data!B22,LookupTables!$A$2:$C$11,3)</f>
-        <v>500</v>
+      <c r="F51" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>15000</v>
       </c>
       <c r="G51">
         <f>VLOOKUP(F51,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H51">
-        <f>F51/2</f>
-        <v>250</v>
-      </c>
-      <c r="I51" s="3">
+        <f t="shared" si="7"/>
+        <v>7500</v>
+      </c>
+      <c r="I51">
         <f>VLOOKUP(H51,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
-      </c>
-      <c r="J51" s="2">
-        <f>F51+D51</f>
-        <v>500</v>
+        <v>23</v>
+      </c>
+      <c r="J51" s="1">
+        <f t="shared" si="8"/>
+        <v>15000</v>
       </c>
       <c r="K51">
         <f>VLOOKUP(J51,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="L51">
-        <f>J51/2</f>
-        <v>250</v>
-      </c>
-      <c r="M51" s="3">
+        <f t="shared" si="9"/>
+        <v>7500</v>
+      </c>
+      <c r="M51">
         <f>VLOOKUP(L51,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="N51">
-        <f>F51/2+D51</f>
-        <v>250</v>
-      </c>
-      <c r="O51" s="3">
+        <f t="shared" si="10"/>
+        <v>7500</v>
+      </c>
+      <c r="O51">
         <f>VLOOKUP(N51,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
-      </c>
-      <c r="P51" s="2">
-        <f>F51+E51+D51</f>
-        <v>600</v>
+        <v>23</v>
+      </c>
+      <c r="P51" s="1">
+        <f t="shared" si="11"/>
+        <v>15100</v>
       </c>
       <c r="Q51">
         <f>VLOOKUP(P51,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="R51">
-        <f>P51/2</f>
-        <v>300</v>
-      </c>
-      <c r="S51" s="3">
+        <f t="shared" si="12"/>
+        <v>7550</v>
+      </c>
+      <c r="S51">
         <f>VLOOKUP(R51,LookupTables!$E$2:$F$18,2)</f>
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="T51">
-        <f>F51/2+E51+D51</f>
-        <v>350</v>
-      </c>
-      <c r="U51" s="3">
+        <f t="shared" si="13"/>
+        <v>7600</v>
+      </c>
+      <c r="U51">
         <f>VLOOKUP(T51,LookupTables!$E$2:$F$18,2)</f>
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.2">
@@ -5178,7 +5177,7 @@
       <c r="B52">
         <v>6</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D52">
@@ -5187,69 +5186,69 @@
       <c r="E52">
         <v>1000</v>
       </c>
-      <c r="F52" s="2">
-        <f>VLOOKUP(Data!B23,LookupTables!$A$2:$C$11,3)</f>
-        <v>500</v>
+      <c r="F52" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>15000</v>
       </c>
       <c r="G52">
         <f>VLOOKUP(F52,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H52">
-        <f>F52/2</f>
-        <v>250</v>
-      </c>
-      <c r="I52" s="3">
+        <f t="shared" si="7"/>
+        <v>7500</v>
+      </c>
+      <c r="I52">
         <f>VLOOKUP(H52,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
-      </c>
-      <c r="J52" s="2">
-        <f>F52+D52</f>
-        <v>500</v>
+        <v>23</v>
+      </c>
+      <c r="J52" s="1">
+        <f t="shared" si="8"/>
+        <v>15000</v>
       </c>
       <c r="K52">
         <f>VLOOKUP(J52,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="L52">
-        <f>J52/2</f>
-        <v>250</v>
-      </c>
-      <c r="M52" s="3">
+        <f t="shared" si="9"/>
+        <v>7500</v>
+      </c>
+      <c r="M52">
         <f>VLOOKUP(L52,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="N52">
-        <f>F52/2+D52</f>
-        <v>250</v>
-      </c>
-      <c r="O52" s="3">
+        <f t="shared" si="10"/>
+        <v>7500</v>
+      </c>
+      <c r="O52">
         <f>VLOOKUP(N52,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
-      </c>
-      <c r="P52" s="2">
-        <f>F52+E52+D52</f>
-        <v>1500</v>
+        <v>23</v>
+      </c>
+      <c r="P52" s="1">
+        <f t="shared" si="11"/>
+        <v>16000</v>
       </c>
       <c r="Q52">
         <f>VLOOKUP(P52,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="R52">
-        <f>P52/2</f>
-        <v>750</v>
-      </c>
-      <c r="S52" s="3">
+        <f t="shared" si="12"/>
+        <v>8000</v>
+      </c>
+      <c r="S52">
         <f>VLOOKUP(R52,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T52">
-        <f>F52/2+E52+D52</f>
-        <v>1250</v>
-      </c>
-      <c r="U52" s="3">
+        <f t="shared" si="13"/>
+        <v>8500</v>
+      </c>
+      <c r="U52">
         <f>VLOOKUP(T52,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.2">
@@ -5259,7 +5258,7 @@
       <c r="B53">
         <v>6</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D53">
@@ -5268,69 +5267,69 @@
       <c r="E53">
         <v>10</v>
       </c>
-      <c r="F53" s="2">
-        <f>VLOOKUP(Data!B28,LookupTables!$A$2:$C$11,3)</f>
-        <v>2500</v>
+      <c r="F53" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>15000</v>
       </c>
       <c r="G53">
         <f>VLOOKUP(F53,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="H53">
-        <f>F53/2</f>
-        <v>1250</v>
-      </c>
-      <c r="I53" s="3">
+        <f t="shared" si="7"/>
+        <v>7500</v>
+      </c>
+      <c r="I53">
         <f>VLOOKUP(H53,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
-      </c>
-      <c r="J53" s="2">
-        <f>F53+D53</f>
-        <v>2500</v>
+        <v>23</v>
+      </c>
+      <c r="J53" s="1">
+        <f t="shared" si="8"/>
+        <v>15000</v>
       </c>
       <c r="K53">
         <f>VLOOKUP(J53,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="L53">
-        <f>J53/2</f>
-        <v>1250</v>
-      </c>
-      <c r="M53" s="3">
+        <f t="shared" si="9"/>
+        <v>7500</v>
+      </c>
+      <c r="M53">
         <f>VLOOKUP(L53,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="N53">
-        <f>F53/2+D53</f>
-        <v>1250</v>
-      </c>
-      <c r="O53" s="3">
+        <f t="shared" si="10"/>
+        <v>7500</v>
+      </c>
+      <c r="O53">
         <f>VLOOKUP(N53,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
-      </c>
-      <c r="P53" s="2">
-        <f>F53+E53+D53</f>
-        <v>2510</v>
+        <v>23</v>
+      </c>
+      <c r="P53" s="1">
+        <f t="shared" si="11"/>
+        <v>15010</v>
       </c>
       <c r="Q53">
         <f>VLOOKUP(P53,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="R53">
-        <f>P53/2</f>
-        <v>1255</v>
-      </c>
-      <c r="S53" s="3">
+        <f t="shared" si="12"/>
+        <v>7505</v>
+      </c>
+      <c r="S53">
         <f>VLOOKUP(R53,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="T53">
-        <f>F53/2+E53+D53</f>
-        <v>1260</v>
-      </c>
-      <c r="U53" s="3">
+        <f t="shared" si="13"/>
+        <v>7510</v>
+      </c>
+      <c r="U53">
         <f>VLOOKUP(T53,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.2">
@@ -5340,7 +5339,7 @@
       <c r="B54">
         <v>6</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="2" t="s">
         <v>104</v>
       </c>
       <c r="D54">
@@ -5349,69 +5348,69 @@
       <c r="E54">
         <v>0</v>
       </c>
-      <c r="F54" s="2">
-        <f>VLOOKUP(Data!B30,LookupTables!$A$2:$C$11,3)</f>
-        <v>2500</v>
+      <c r="F54" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>15000</v>
       </c>
       <c r="G54">
         <f>VLOOKUP(F54,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="H54">
-        <f>F54/2</f>
-        <v>1250</v>
-      </c>
-      <c r="I54" s="3">
+        <f t="shared" si="7"/>
+        <v>7500</v>
+      </c>
+      <c r="I54">
         <f>VLOOKUP(H54,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
-      </c>
-      <c r="J54" s="2">
-        <f>F54+D54</f>
-        <v>3500</v>
+        <v>23</v>
+      </c>
+      <c r="J54" s="1">
+        <f t="shared" si="8"/>
+        <v>16000</v>
       </c>
       <c r="K54">
         <f>VLOOKUP(J54,LookupTables!$E$2:$F$18,2)</f>
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L54">
-        <f>J54/2</f>
-        <v>1750</v>
-      </c>
-      <c r="M54" s="3">
+        <f t="shared" si="9"/>
+        <v>8000</v>
+      </c>
+      <c r="M54">
         <f>VLOOKUP(L54,LookupTables!$E$2:$F$18,2)</f>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="N54">
-        <f>F54/2+D54</f>
-        <v>2250</v>
-      </c>
-      <c r="O54" s="3">
+        <f t="shared" si="10"/>
+        <v>8500</v>
+      </c>
+      <c r="O54">
         <f>VLOOKUP(N54,LookupTables!$E$2:$F$18,2)</f>
-        <v>15</v>
-      </c>
-      <c r="P54" s="2">
-        <f>F54+E54+D54</f>
-        <v>3500</v>
+        <v>25</v>
+      </c>
+      <c r="P54" s="1">
+        <f t="shared" si="11"/>
+        <v>16000</v>
       </c>
       <c r="Q54">
         <f>VLOOKUP(P54,LookupTables!$E$2:$F$18,2)</f>
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="R54">
-        <f>P54/2</f>
-        <v>1750</v>
-      </c>
-      <c r="S54" s="3">
+        <f t="shared" si="12"/>
+        <v>8000</v>
+      </c>
+      <c r="S54">
         <f>VLOOKUP(R54,LookupTables!$E$2:$F$18,2)</f>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="T54">
-        <f>F54/2+E54+D54</f>
-        <v>2250</v>
-      </c>
-      <c r="U54" s="3">
+        <f t="shared" si="13"/>
+        <v>8500</v>
+      </c>
+      <c r="U54">
         <f>VLOOKUP(T54,LookupTables!$E$2:$F$18,2)</f>
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.2">
@@ -5421,7 +5420,7 @@
       <c r="B55">
         <v>6</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="2" t="s">
         <v>114</v>
       </c>
       <c r="D55">
@@ -5430,69 +5429,69 @@
       <c r="E55">
         <v>500</v>
       </c>
-      <c r="F55" s="2">
-        <f>VLOOKUP(Data!B40,LookupTables!$A$2:$C$11,3)</f>
-        <v>5000</v>
+      <c r="F55" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>15000</v>
       </c>
       <c r="G55">
         <f>VLOOKUP(F55,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H55">
-        <f>F55/2</f>
-        <v>2500</v>
-      </c>
-      <c r="I55" s="3">
+        <f t="shared" si="7"/>
+        <v>7500</v>
+      </c>
+      <c r="I55">
         <f>VLOOKUP(H55,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="J55" s="2">
-        <f>F55+D55</f>
-        <v>5000</v>
+        <v>23</v>
+      </c>
+      <c r="J55" s="1">
+        <f t="shared" si="8"/>
+        <v>15000</v>
       </c>
       <c r="K55">
         <f>VLOOKUP(J55,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L55">
-        <f>J55/2</f>
-        <v>2500</v>
-      </c>
-      <c r="M55" s="3">
+        <f t="shared" si="9"/>
+        <v>7500</v>
+      </c>
+      <c r="M55">
         <f>VLOOKUP(L55,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="N55">
-        <f>F55/2+D55</f>
-        <v>2500</v>
-      </c>
-      <c r="O55" s="3">
+        <f t="shared" si="10"/>
+        <v>7500</v>
+      </c>
+      <c r="O55">
         <f>VLOOKUP(N55,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="P55" s="2">
-        <f>F55+E55+D55</f>
-        <v>5500</v>
+        <v>23</v>
+      </c>
+      <c r="P55" s="1">
+        <f t="shared" si="11"/>
+        <v>15500</v>
       </c>
       <c r="Q55">
         <f>VLOOKUP(P55,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R55">
-        <f>P55/2</f>
-        <v>2750</v>
-      </c>
-      <c r="S55" s="3">
+        <f t="shared" si="12"/>
+        <v>7750</v>
+      </c>
+      <c r="S55">
         <f>VLOOKUP(R55,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="T55">
-        <f>F55/2+E55+D55</f>
-        <v>3000</v>
-      </c>
-      <c r="U55" s="3">
+        <f t="shared" si="13"/>
+        <v>8000</v>
+      </c>
+      <c r="U55">
         <f>VLOOKUP(T55,LookupTables!$E$2:$F$18,2)</f>
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.2">
@@ -5502,7 +5501,7 @@
       <c r="B56">
         <v>6</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="2" t="s">
         <v>121</v>
       </c>
       <c r="D56">
@@ -5511,8 +5510,8 @@
       <c r="E56">
         <v>25</v>
       </c>
-      <c r="F56" s="2">
-        <f>VLOOKUP(Data!B47,LookupTables!$A$2:$C$11,3)</f>
+      <c r="F56" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
         <v>15000</v>
       </c>
       <c r="G56">
@@ -5520,15 +5519,15 @@
         <v>27</v>
       </c>
       <c r="H56">
-        <f>F56/2</f>
+        <f t="shared" si="7"/>
         <v>7500</v>
       </c>
-      <c r="I56" s="3">
+      <c r="I56">
         <f>VLOOKUP(H56,LookupTables!$E$2:$F$18,2)</f>
         <v>23</v>
       </c>
-      <c r="J56" s="2">
-        <f>F56+D56</f>
+      <c r="J56" s="1">
+        <f t="shared" si="8"/>
         <v>15000</v>
       </c>
       <c r="K56">
@@ -5536,23 +5535,23 @@
         <v>27</v>
       </c>
       <c r="L56">
-        <f>J56/2</f>
+        <f t="shared" si="9"/>
         <v>7500</v>
       </c>
-      <c r="M56" s="3">
+      <c r="M56">
         <f>VLOOKUP(L56,LookupTables!$E$2:$F$18,2)</f>
         <v>23</v>
       </c>
       <c r="N56">
-        <f>F56/2+D56</f>
+        <f t="shared" si="10"/>
         <v>7500</v>
       </c>
-      <c r="O56" s="3">
+      <c r="O56">
         <f>VLOOKUP(N56,LookupTables!$E$2:$F$18,2)</f>
         <v>23</v>
       </c>
-      <c r="P56" s="2">
-        <f>F56+E56+D56</f>
+      <c r="P56" s="1">
+        <f t="shared" si="11"/>
         <v>15025</v>
       </c>
       <c r="Q56">
@@ -5560,18 +5559,18 @@
         <v>27</v>
       </c>
       <c r="R56">
-        <f>P56/2</f>
+        <f t="shared" si="12"/>
         <v>7512.5</v>
       </c>
-      <c r="S56" s="3">
+      <c r="S56">
         <f>VLOOKUP(R56,LookupTables!$E$2:$F$18,2)</f>
         <v>23</v>
       </c>
       <c r="T56">
-        <f>F56/2+E56+D56</f>
+        <f t="shared" si="13"/>
         <v>7525</v>
       </c>
-      <c r="U56" s="3">
+      <c r="U56">
         <f>VLOOKUP(T56,LookupTables!$E$2:$F$18,2)</f>
         <v>23</v>
       </c>
@@ -5583,7 +5582,7 @@
       <c r="B57">
         <v>6</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="2" t="s">
         <v>139</v>
       </c>
       <c r="D57">
@@ -5592,69 +5591,69 @@
       <c r="E57">
         <v>600</v>
       </c>
-      <c r="F57" s="2">
-        <f>VLOOKUP(Data!B67,LookupTables!$A$2:$C$11,3)</f>
-        <v>25000</v>
+      <c r="F57" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>15000</v>
       </c>
       <c r="G57">
         <f>VLOOKUP(F57,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H57">
-        <f>F57/2</f>
-        <v>12500</v>
-      </c>
-      <c r="I57" s="3">
+        <f t="shared" si="7"/>
+        <v>7500</v>
+      </c>
+      <c r="I57">
         <f>VLOOKUP(H57,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
-      </c>
-      <c r="J57" s="2">
-        <f>F57+D57</f>
-        <v>25000</v>
+        <v>23</v>
+      </c>
+      <c r="J57" s="1">
+        <f t="shared" si="8"/>
+        <v>15000</v>
       </c>
       <c r="K57">
         <f>VLOOKUP(J57,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L57">
-        <f>J57/2</f>
-        <v>12500</v>
-      </c>
-      <c r="M57" s="3">
+        <f t="shared" si="9"/>
+        <v>7500</v>
+      </c>
+      <c r="M57">
         <f>VLOOKUP(L57,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N57">
-        <f>F57/2+D57</f>
-        <v>12500</v>
-      </c>
-      <c r="O57" s="3">
+        <f t="shared" si="10"/>
+        <v>7500</v>
+      </c>
+      <c r="O57">
         <f>VLOOKUP(N57,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
-      </c>
-      <c r="P57" s="2">
-        <f>F57+E57+D57</f>
-        <v>25600</v>
+        <v>23</v>
+      </c>
+      <c r="P57" s="1">
+        <f t="shared" si="11"/>
+        <v>15600</v>
       </c>
       <c r="Q57">
         <f>VLOOKUP(P57,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R57">
-        <f>P57/2</f>
-        <v>12800</v>
-      </c>
-      <c r="S57" s="3">
+        <f t="shared" si="12"/>
+        <v>7800</v>
+      </c>
+      <c r="S57">
         <f>VLOOKUP(R57,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="T57">
-        <f>F57/2+E57+D57</f>
-        <v>13100</v>
-      </c>
-      <c r="U57" s="3">
+        <f t="shared" si="13"/>
+        <v>8100</v>
+      </c>
+      <c r="U57">
         <f>VLOOKUP(T57,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.2">
@@ -5664,7 +5663,7 @@
       <c r="B58">
         <v>6</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="2" t="s">
         <v>143</v>
       </c>
       <c r="D58">
@@ -5673,69 +5672,69 @@
       <c r="E58">
         <v>500</v>
       </c>
-      <c r="F58" s="2">
-        <f>VLOOKUP(Data!B71,LookupTables!$A$2:$C$11,3)</f>
-        <v>250000</v>
+      <c r="F58" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>15000</v>
       </c>
       <c r="G58">
         <f>VLOOKUP(F58,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H58">
-        <f>F58/2</f>
-        <v>125000</v>
-      </c>
-      <c r="I58" s="3">
+        <f t="shared" si="7"/>
+        <v>7500</v>
+      </c>
+      <c r="I58">
         <f>VLOOKUP(H58,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
-      </c>
-      <c r="J58" s="2">
-        <f>F58+D58</f>
-        <v>250000</v>
+        <v>23</v>
+      </c>
+      <c r="J58" s="1">
+        <f t="shared" si="8"/>
+        <v>15000</v>
       </c>
       <c r="K58">
         <f>VLOOKUP(J58,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L58">
-        <f>J58/2</f>
-        <v>125000</v>
-      </c>
-      <c r="M58" s="3">
+        <f t="shared" si="9"/>
+        <v>7500</v>
+      </c>
+      <c r="M58">
         <f>VLOOKUP(L58,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="N58">
-        <f>F58/2+D58</f>
-        <v>125000</v>
-      </c>
-      <c r="O58" s="3">
+        <f t="shared" si="10"/>
+        <v>7500</v>
+      </c>
+      <c r="O58">
         <f>VLOOKUP(N58,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
-      </c>
-      <c r="P58" s="2">
-        <f>F58+E58+D58</f>
-        <v>250500</v>
+        <v>23</v>
+      </c>
+      <c r="P58" s="1">
+        <f t="shared" si="11"/>
+        <v>15500</v>
       </c>
       <c r="Q58">
         <f>VLOOKUP(P58,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R58">
-        <f>P58/2</f>
-        <v>125250</v>
-      </c>
-      <c r="S58" s="3">
+        <f t="shared" si="12"/>
+        <v>7750</v>
+      </c>
+      <c r="S58">
         <f>VLOOKUP(R58,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="T58">
-        <f>F58/2+E58+D58</f>
-        <v>125500</v>
-      </c>
-      <c r="U58" s="3">
+        <f t="shared" si="13"/>
+        <v>8000</v>
+      </c>
+      <c r="U58">
         <f>VLOOKUP(T58,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.2">
@@ -5745,7 +5744,7 @@
       <c r="B59">
         <v>6</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="2" t="s">
         <v>146</v>
       </c>
       <c r="D59">
@@ -5754,69 +5753,69 @@
       <c r="E59">
         <v>0</v>
       </c>
-      <c r="F59" s="2">
-        <f>VLOOKUP(Data!B74,LookupTables!$A$2:$C$11,3)</f>
-        <v>250000</v>
+      <c r="F59" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>15000</v>
       </c>
       <c r="G59">
         <f>VLOOKUP(F59,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H59">
-        <f>F59/2</f>
-        <v>125000</v>
-      </c>
-      <c r="I59" s="3">
+        <f t="shared" si="7"/>
+        <v>7500</v>
+      </c>
+      <c r="I59">
         <f>VLOOKUP(H59,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
-      </c>
-      <c r="J59" s="2">
-        <f>F59+D59</f>
-        <v>250025</v>
+        <v>23</v>
+      </c>
+      <c r="J59" s="1">
+        <f t="shared" si="8"/>
+        <v>15025</v>
       </c>
       <c r="K59">
         <f>VLOOKUP(J59,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L59">
-        <f>J59/2</f>
-        <v>125012.5</v>
-      </c>
-      <c r="M59" s="3">
+        <f t="shared" si="9"/>
+        <v>7512.5</v>
+      </c>
+      <c r="M59">
         <f>VLOOKUP(L59,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="N59">
-        <f>F59/2+D59</f>
-        <v>125025</v>
-      </c>
-      <c r="O59" s="3">
+        <f t="shared" si="10"/>
+        <v>7525</v>
+      </c>
+      <c r="O59">
         <f>VLOOKUP(N59,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
-      </c>
-      <c r="P59" s="2">
-        <f>F59+E59+D59</f>
-        <v>250025</v>
+        <v>23</v>
+      </c>
+      <c r="P59" s="1">
+        <f t="shared" si="11"/>
+        <v>15025</v>
       </c>
       <c r="Q59">
         <f>VLOOKUP(P59,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R59">
-        <f>P59/2</f>
-        <v>125012.5</v>
-      </c>
-      <c r="S59" s="3">
+        <f t="shared" si="12"/>
+        <v>7512.5</v>
+      </c>
+      <c r="S59">
         <f>VLOOKUP(R59,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="T59">
-        <f>F59/2+E59+D59</f>
-        <v>125025</v>
-      </c>
-      <c r="U59" s="3">
+        <f t="shared" si="13"/>
+        <v>7525</v>
+      </c>
+      <c r="U59">
         <f>VLOOKUP(T59,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.2">
@@ -5826,75 +5825,75 @@
       <c r="B60">
         <v>7</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D60">
         <v>1500</v>
       </c>
-      <c r="F60" s="2">
-        <f>VLOOKUP(Data!B24,LookupTables!$A$2:$C$11,3)</f>
-        <v>500</v>
+      <c r="F60" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>25000</v>
       </c>
       <c r="G60">
         <f>VLOOKUP(F60,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="H60">
-        <f>F60/2</f>
-        <v>250</v>
-      </c>
-      <c r="I60" s="3">
+        <f t="shared" si="7"/>
+        <v>12500</v>
+      </c>
+      <c r="I60">
         <f>VLOOKUP(H60,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
-      </c>
-      <c r="J60" s="2">
-        <f>F60+D60</f>
-        <v>2000</v>
+        <v>27</v>
+      </c>
+      <c r="J60" s="1">
+        <f t="shared" si="8"/>
+        <v>26500</v>
       </c>
       <c r="K60">
         <f>VLOOKUP(J60,LookupTables!$E$2:$F$18,2)</f>
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="L60">
-        <f>J60/2</f>
-        <v>1000</v>
-      </c>
-      <c r="M60" s="3">
+        <f t="shared" si="9"/>
+        <v>13250</v>
+      </c>
+      <c r="M60">
         <f>VLOOKUP(L60,LookupTables!$E$2:$F$18,2)</f>
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="N60">
-        <f>F60/2+D60</f>
-        <v>1750</v>
-      </c>
-      <c r="O60" s="3">
+        <f t="shared" si="10"/>
+        <v>14000</v>
+      </c>
+      <c r="O60">
         <f>VLOOKUP(N60,LookupTables!$E$2:$F$18,2)</f>
-        <v>13</v>
-      </c>
-      <c r="P60" s="2">
-        <f>F60+E60+D60</f>
-        <v>2000</v>
+        <v>27</v>
+      </c>
+      <c r="P60" s="1">
+        <f t="shared" si="11"/>
+        <v>26500</v>
       </c>
       <c r="Q60">
         <f>VLOOKUP(P60,LookupTables!$E$2:$F$18,2)</f>
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="R60">
-        <f>P60/2</f>
-        <v>1000</v>
-      </c>
-      <c r="S60" s="3">
+        <f t="shared" si="12"/>
+        <v>13250</v>
+      </c>
+      <c r="S60">
         <f>VLOOKUP(R60,LookupTables!$E$2:$F$18,2)</f>
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="T60">
-        <f>F60/2+E60+D60</f>
-        <v>1750</v>
-      </c>
-      <c r="U60" s="3">
+        <f t="shared" si="13"/>
+        <v>14000</v>
+      </c>
+      <c r="U60">
         <f>VLOOKUP(T60,LookupTables!$E$2:$F$18,2)</f>
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.2">
@@ -5904,7 +5903,7 @@
       <c r="B61">
         <v>7</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="2" t="s">
         <v>116</v>
       </c>
       <c r="D61">
@@ -5913,69 +5912,69 @@
       <c r="E61">
         <v>15</v>
       </c>
-      <c r="F61" s="2">
-        <f>VLOOKUP(Data!B42,LookupTables!$A$2:$C$11,3)</f>
-        <v>5000</v>
+      <c r="F61" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>25000</v>
       </c>
       <c r="G61">
         <f>VLOOKUP(F61,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H61">
-        <f>F61/2</f>
-        <v>2500</v>
-      </c>
-      <c r="I61" s="3">
+        <f t="shared" si="7"/>
+        <v>12500</v>
+      </c>
+      <c r="I61">
         <f>VLOOKUP(H61,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="J61" s="2">
-        <f>F61+D61</f>
-        <v>5000</v>
+        <v>27</v>
+      </c>
+      <c r="J61" s="1">
+        <f t="shared" si="8"/>
+        <v>25000</v>
       </c>
       <c r="K61">
         <f>VLOOKUP(J61,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="L61">
-        <f>J61/2</f>
-        <v>2500</v>
-      </c>
-      <c r="M61" s="3">
+        <f t="shared" si="9"/>
+        <v>12500</v>
+      </c>
+      <c r="M61">
         <f>VLOOKUP(L61,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="N61">
-        <f>F61/2+D61</f>
-        <v>2500</v>
-      </c>
-      <c r="O61" s="3">
+        <f t="shared" si="10"/>
+        <v>12500</v>
+      </c>
+      <c r="O61">
         <f>VLOOKUP(N61,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="P61" s="2">
-        <f>F61+E61+D61</f>
-        <v>5015</v>
+        <v>27</v>
+      </c>
+      <c r="P61" s="1">
+        <f t="shared" si="11"/>
+        <v>25015</v>
       </c>
       <c r="Q61">
         <f>VLOOKUP(P61,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="R61">
-        <f>P61/2</f>
-        <v>2507.5</v>
-      </c>
-      <c r="S61" s="3">
+        <f t="shared" si="12"/>
+        <v>12507.5</v>
+      </c>
+      <c r="S61">
         <f>VLOOKUP(R61,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="T61">
-        <f>F61/2+E61+D61</f>
-        <v>2515</v>
-      </c>
-      <c r="U61" s="3">
+        <f t="shared" si="13"/>
+        <v>12515</v>
+      </c>
+      <c r="U61">
         <f>VLOOKUP(T61,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.2">
@@ -5985,7 +5984,7 @@
       <c r="B62">
         <v>7</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D62">
@@ -5994,69 +5993,69 @@
       <c r="E62">
         <v>250</v>
       </c>
-      <c r="F62" s="2">
-        <f>VLOOKUP(Data!B43,LookupTables!$A$2:$C$11,3)</f>
-        <v>5000</v>
+      <c r="F62" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>25000</v>
       </c>
       <c r="G62">
         <f>VLOOKUP(F62,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H62">
-        <f>F62/2</f>
-        <v>2500</v>
-      </c>
-      <c r="I62" s="3">
+        <f t="shared" si="7"/>
+        <v>12500</v>
+      </c>
+      <c r="I62">
         <f>VLOOKUP(H62,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="J62" s="2">
-        <f>F62+D62</f>
-        <v>5000</v>
+        <v>27</v>
+      </c>
+      <c r="J62" s="1">
+        <f t="shared" si="8"/>
+        <v>25000</v>
       </c>
       <c r="K62">
         <f>VLOOKUP(J62,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="L62">
-        <f>J62/2</f>
-        <v>2500</v>
-      </c>
-      <c r="M62" s="3">
+        <f t="shared" si="9"/>
+        <v>12500</v>
+      </c>
+      <c r="M62">
         <f>VLOOKUP(L62,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="N62">
-        <f>F62/2+D62</f>
-        <v>2500</v>
-      </c>
-      <c r="O62" s="3">
+        <f t="shared" si="10"/>
+        <v>12500</v>
+      </c>
+      <c r="O62">
         <f>VLOOKUP(N62,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="P62" s="2">
-        <f>F62+E62+D62</f>
-        <v>5250</v>
+        <v>27</v>
+      </c>
+      <c r="P62" s="1">
+        <f t="shared" si="11"/>
+        <v>25250</v>
       </c>
       <c r="Q62">
         <f>VLOOKUP(P62,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="R62">
-        <f>P62/2</f>
-        <v>2625</v>
-      </c>
-      <c r="S62" s="3">
+        <f t="shared" si="12"/>
+        <v>12625</v>
+      </c>
+      <c r="S62">
         <f>VLOOKUP(R62,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="T62">
-        <f>F62/2+E62+D62</f>
-        <v>2750</v>
-      </c>
-      <c r="U62" s="3">
+        <f t="shared" si="13"/>
+        <v>12750</v>
+      </c>
+      <c r="U62">
         <f>VLOOKUP(T62,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
@@ -6066,7 +6065,7 @@
       <c r="B63">
         <v>7</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D63">
@@ -6075,69 +6074,69 @@
       <c r="E63">
         <v>250</v>
       </c>
-      <c r="F63" s="2">
-        <f>VLOOKUP(Data!B46,LookupTables!$A$2:$C$11,3)</f>
-        <v>15000</v>
+      <c r="F63" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>25000</v>
       </c>
       <c r="G63">
         <f>VLOOKUP(F63,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H63">
-        <f>F63/2</f>
-        <v>7500</v>
-      </c>
-      <c r="I63" s="3">
+        <f t="shared" si="7"/>
+        <v>12500</v>
+      </c>
+      <c r="I63">
         <f>VLOOKUP(H63,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="J63" s="2">
-        <f>F63+D63</f>
-        <v>15000</v>
+        <v>27</v>
+      </c>
+      <c r="J63" s="1">
+        <f t="shared" si="8"/>
+        <v>25000</v>
       </c>
       <c r="K63">
         <f>VLOOKUP(J63,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L63">
-        <f>J63/2</f>
-        <v>7500</v>
-      </c>
-      <c r="M63" s="3">
+        <f t="shared" si="9"/>
+        <v>12500</v>
+      </c>
+      <c r="M63">
         <f>VLOOKUP(L63,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="N63">
-        <f>F63/2+D63</f>
-        <v>7500</v>
-      </c>
-      <c r="O63" s="3">
+        <f t="shared" si="10"/>
+        <v>12500</v>
+      </c>
+      <c r="O63">
         <f>VLOOKUP(N63,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="P63" s="2">
-        <f>F63+E63+D63</f>
-        <v>15250</v>
+        <v>27</v>
+      </c>
+      <c r="P63" s="1">
+        <f t="shared" si="11"/>
+        <v>25250</v>
       </c>
       <c r="Q63">
         <f>VLOOKUP(P63,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R63">
-        <f>P63/2</f>
-        <v>7625</v>
-      </c>
-      <c r="S63" s="3">
+        <f t="shared" si="12"/>
+        <v>12625</v>
+      </c>
+      <c r="S63">
         <f>VLOOKUP(R63,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="T63">
-        <f>F63/2+E63+D63</f>
-        <v>7750</v>
-      </c>
-      <c r="U63" s="3">
+        <f t="shared" si="13"/>
+        <v>12750</v>
+      </c>
+      <c r="U63">
         <f>VLOOKUP(T63,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.2">
@@ -6147,7 +6146,7 @@
       <c r="B64">
         <v>7</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="2" t="s">
         <v>122</v>
       </c>
       <c r="D64">
@@ -6156,69 +6155,69 @@
       <c r="E64">
         <v>5</v>
       </c>
-      <c r="F64" s="2">
-        <f>VLOOKUP(Data!B48,LookupTables!$A$2:$C$11,3)</f>
-        <v>15000</v>
+      <c r="F64" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>25000</v>
       </c>
       <c r="G64">
         <f>VLOOKUP(F64,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H64">
-        <f>F64/2</f>
-        <v>7500</v>
-      </c>
-      <c r="I64" s="3">
+        <f t="shared" si="7"/>
+        <v>12500</v>
+      </c>
+      <c r="I64">
         <f>VLOOKUP(H64,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="J64" s="2">
-        <f>F64+D64</f>
-        <v>15000</v>
+        <v>27</v>
+      </c>
+      <c r="J64" s="1">
+        <f t="shared" si="8"/>
+        <v>25000</v>
       </c>
       <c r="K64">
         <f>VLOOKUP(J64,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L64">
-        <f>J64/2</f>
-        <v>7500</v>
-      </c>
-      <c r="M64" s="3">
+        <f t="shared" si="9"/>
+        <v>12500</v>
+      </c>
+      <c r="M64">
         <f>VLOOKUP(L64,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="N64">
-        <f>F64/2+D64</f>
-        <v>7500</v>
-      </c>
-      <c r="O64" s="3">
+        <f t="shared" si="10"/>
+        <v>12500</v>
+      </c>
+      <c r="O64">
         <f>VLOOKUP(N64,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="P64" s="2">
-        <f>F64+E64+D64</f>
-        <v>15005</v>
+        <v>27</v>
+      </c>
+      <c r="P64" s="1">
+        <f t="shared" si="11"/>
+        <v>25005</v>
       </c>
       <c r="Q64">
         <f>VLOOKUP(P64,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R64">
-        <f>P64/2</f>
-        <v>7502.5</v>
-      </c>
-      <c r="S64" s="3">
+        <f t="shared" si="12"/>
+        <v>12502.5</v>
+      </c>
+      <c r="S64">
         <f>VLOOKUP(R64,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="T64">
-        <f>F64/2+E64+D64</f>
-        <v>7505</v>
-      </c>
-      <c r="U64" s="3">
+        <f t="shared" si="13"/>
+        <v>12505</v>
+      </c>
+      <c r="U64">
         <f>VLOOKUP(T64,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.2">
@@ -6228,7 +6227,7 @@
       <c r="B65">
         <v>7</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="2" t="s">
         <v>126</v>
       </c>
       <c r="D65">
@@ -6237,69 +6236,69 @@
       <c r="E65">
         <v>0</v>
       </c>
-      <c r="F65" s="2">
-        <f>VLOOKUP(Data!B52,LookupTables!$A$2:$C$11,3)</f>
-        <v>15000</v>
+      <c r="F65" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>25000</v>
       </c>
       <c r="G65">
         <f>VLOOKUP(F65,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H65">
-        <f>F65/2</f>
-        <v>7500</v>
-      </c>
-      <c r="I65" s="3">
+        <f t="shared" si="7"/>
+        <v>12500</v>
+      </c>
+      <c r="I65">
         <f>VLOOKUP(H65,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="J65" s="2">
-        <f>F65+D65</f>
-        <v>16000</v>
+        <v>27</v>
+      </c>
+      <c r="J65" s="1">
+        <f t="shared" si="8"/>
+        <v>26000</v>
       </c>
       <c r="K65">
         <f>VLOOKUP(J65,LookupTables!$E$2:$F$18,2)</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L65">
-        <f>J65/2</f>
-        <v>8000</v>
-      </c>
-      <c r="M65" s="3">
+        <f t="shared" si="9"/>
+        <v>13000</v>
+      </c>
+      <c r="M65">
         <f>VLOOKUP(L65,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N65">
-        <f>F65/2+D65</f>
-        <v>8500</v>
-      </c>
-      <c r="O65" s="3">
+        <f t="shared" si="10"/>
+        <v>13500</v>
+      </c>
+      <c r="O65">
         <f>VLOOKUP(N65,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
-      </c>
-      <c r="P65" s="2">
-        <f>F65+E65+D65</f>
-        <v>16000</v>
+        <v>27</v>
+      </c>
+      <c r="P65" s="1">
+        <f t="shared" si="11"/>
+        <v>26000</v>
       </c>
       <c r="Q65">
         <f>VLOOKUP(P65,LookupTables!$E$2:$F$18,2)</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R65">
-        <f>P65/2</f>
-        <v>8000</v>
-      </c>
-      <c r="S65" s="3">
+        <f t="shared" si="12"/>
+        <v>13000</v>
+      </c>
+      <c r="S65">
         <f>VLOOKUP(R65,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="T65">
-        <f>F65/2+E65+D65</f>
-        <v>8500</v>
-      </c>
-      <c r="U65" s="3">
+        <f t="shared" si="13"/>
+        <v>13500</v>
+      </c>
+      <c r="U65">
         <f>VLOOKUP(T65,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.2">
@@ -6309,7 +6308,7 @@
       <c r="B66">
         <v>7</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D66">
@@ -6318,69 +6317,69 @@
       <c r="E66">
         <v>0</v>
       </c>
-      <c r="F66" s="2">
-        <f>VLOOKUP(Data!B55,LookupTables!$A$2:$C$11,3)</f>
-        <v>15000</v>
+      <c r="F66" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>25000</v>
       </c>
       <c r="G66">
         <f>VLOOKUP(F66,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H66">
-        <f>F66/2</f>
-        <v>7500</v>
-      </c>
-      <c r="I66" s="3">
+        <f t="shared" si="7"/>
+        <v>12500</v>
+      </c>
+      <c r="I66">
         <f>VLOOKUP(H66,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="J66" s="2">
-        <f>F66+D66</f>
-        <v>20000</v>
+        <v>27</v>
+      </c>
+      <c r="J66" s="1">
+        <f t="shared" si="8"/>
+        <v>30000</v>
       </c>
       <c r="K66">
         <f>VLOOKUP(J66,LookupTables!$E$2:$F$18,2)</f>
         <v>31</v>
       </c>
       <c r="L66">
-        <f>J66/2</f>
-        <v>10000</v>
-      </c>
-      <c r="M66" s="3">
+        <f t="shared" si="9"/>
+        <v>15000</v>
+      </c>
+      <c r="M66">
         <f>VLOOKUP(L66,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N66">
-        <f>F66/2+D66</f>
-        <v>12500</v>
-      </c>
-      <c r="O66" s="3">
+        <f t="shared" si="10"/>
+        <v>17500</v>
+      </c>
+      <c r="O66">
         <f>VLOOKUP(N66,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
-      </c>
-      <c r="P66" s="2">
-        <f>F66+E66+D66</f>
-        <v>20000</v>
+        <v>29</v>
+      </c>
+      <c r="P66" s="1">
+        <f t="shared" si="11"/>
+        <v>30000</v>
       </c>
       <c r="Q66">
         <f>VLOOKUP(P66,LookupTables!$E$2:$F$18,2)</f>
         <v>31</v>
       </c>
       <c r="R66">
-        <f>P66/2</f>
-        <v>10000</v>
-      </c>
-      <c r="S66" s="3">
+        <f t="shared" si="12"/>
+        <v>15000</v>
+      </c>
+      <c r="S66">
         <f>VLOOKUP(R66,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="T66">
-        <f>F66/2+E66+D66</f>
-        <v>12500</v>
-      </c>
-      <c r="U66" s="3">
+        <f t="shared" si="13"/>
+        <v>17500</v>
+      </c>
+      <c r="U66">
         <f>VLOOKUP(T66,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.2">
@@ -6390,7 +6389,7 @@
       <c r="B67">
         <v>7</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C67" s="2" t="s">
         <v>131</v>
       </c>
       <c r="D67">
@@ -6399,69 +6398,69 @@
       <c r="E67">
         <v>0</v>
       </c>
-      <c r="F67" s="2">
-        <f>VLOOKUP(Data!B57,LookupTables!$A$2:$C$11,3)</f>
-        <v>15000</v>
+      <c r="F67" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>25000</v>
       </c>
       <c r="G67">
         <f>VLOOKUP(F67,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H67">
-        <f>F67/2</f>
-        <v>7500</v>
-      </c>
-      <c r="I67" s="3">
+        <f t="shared" ref="H67:H75" si="14">F67/2</f>
+        <v>12500</v>
+      </c>
+      <c r="I67">
         <f>VLOOKUP(H67,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="J67" s="2">
-        <f>F67+D67</f>
-        <v>16500</v>
+        <v>27</v>
+      </c>
+      <c r="J67" s="1">
+        <f t="shared" ref="J67:J75" si="15">F67+D67</f>
+        <v>26500</v>
       </c>
       <c r="K67">
         <f>VLOOKUP(J67,LookupTables!$E$2:$F$18,2)</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L67">
-        <f>J67/2</f>
-        <v>8250</v>
-      </c>
-      <c r="M67" s="3">
+        <f t="shared" ref="L67:L75" si="16">J67/2</f>
+        <v>13250</v>
+      </c>
+      <c r="M67">
         <f>VLOOKUP(L67,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N67">
-        <f>F67/2+D67</f>
-        <v>9000</v>
-      </c>
-      <c r="O67" s="3">
+        <f t="shared" ref="N67:N75" si="17">F67/2+D67</f>
+        <v>14000</v>
+      </c>
+      <c r="O67">
         <f>VLOOKUP(N67,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
-      </c>
-      <c r="P67" s="2">
-        <f>F67+E67+D67</f>
-        <v>16500</v>
+        <v>27</v>
+      </c>
+      <c r="P67" s="1">
+        <f t="shared" ref="P67:P75" si="18">F67+E67+D67</f>
+        <v>26500</v>
       </c>
       <c r="Q67">
         <f>VLOOKUP(P67,LookupTables!$E$2:$F$18,2)</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R67">
-        <f>P67/2</f>
-        <v>8250</v>
-      </c>
-      <c r="S67" s="3">
+        <f t="shared" ref="R67:R75" si="19">P67/2</f>
+        <v>13250</v>
+      </c>
+      <c r="S67">
         <f>VLOOKUP(R67,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="T67">
-        <f>F67/2+E67+D67</f>
-        <v>9000</v>
-      </c>
-      <c r="U67" s="3">
+        <f t="shared" ref="T67:T75" si="20">F67/2+E67+D67</f>
+        <v>14000</v>
+      </c>
+      <c r="U67">
         <f>VLOOKUP(T67,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.2">
@@ -6471,7 +6470,7 @@
       <c r="B68">
         <v>7</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="2" t="s">
         <v>142</v>
       </c>
       <c r="D68">
@@ -6480,69 +6479,69 @@
       <c r="E68">
         <v>0</v>
       </c>
-      <c r="F68" s="2">
-        <f>VLOOKUP(Data!B70,LookupTables!$A$2:$C$11,3)</f>
-        <v>50000</v>
+      <c r="F68" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>25000</v>
       </c>
       <c r="G68">
         <f>VLOOKUP(F68,LookupTables!$E$2:$F$18,2)</f>
         <v>31</v>
       </c>
       <c r="H68">
-        <f>F68/2</f>
-        <v>25000</v>
-      </c>
-      <c r="I68" s="3">
+        <f t="shared" si="14"/>
+        <v>12500</v>
+      </c>
+      <c r="I68">
         <f>VLOOKUP(H68,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
-      </c>
-      <c r="J68" s="2">
-        <f>F68+D68</f>
-        <v>51000</v>
+        <v>27</v>
+      </c>
+      <c r="J68" s="1">
+        <f t="shared" si="15"/>
+        <v>26000</v>
       </c>
       <c r="K68">
         <f>VLOOKUP(J68,LookupTables!$E$2:$F$18,2)</f>
         <v>31</v>
       </c>
       <c r="L68">
-        <f>J68/2</f>
-        <v>25500</v>
-      </c>
-      <c r="M68" s="3">
+        <f t="shared" si="16"/>
+        <v>13000</v>
+      </c>
+      <c r="M68">
         <f>VLOOKUP(L68,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="N68">
-        <f>F68/2+D68</f>
+        <f t="shared" si="17"/>
+        <v>13500</v>
+      </c>
+      <c r="O68">
+        <f>VLOOKUP(N68,LookupTables!$E$2:$F$18,2)</f>
+        <v>27</v>
+      </c>
+      <c r="P68" s="1">
+        <f t="shared" si="18"/>
         <v>26000</v>
-      </c>
-      <c r="O68" s="3">
-        <f>VLOOKUP(N68,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
-      </c>
-      <c r="P68" s="2">
-        <f>F68+E68+D68</f>
-        <v>51000</v>
       </c>
       <c r="Q68">
         <f>VLOOKUP(P68,LookupTables!$E$2:$F$18,2)</f>
         <v>31</v>
       </c>
       <c r="R68">
-        <f>P68/2</f>
-        <v>25500</v>
-      </c>
-      <c r="S68" s="3">
+        <f t="shared" si="19"/>
+        <v>13000</v>
+      </c>
+      <c r="S68">
         <f>VLOOKUP(R68,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="T68">
-        <f>F68/2+E68+D68</f>
-        <v>26000</v>
-      </c>
-      <c r="U68" s="3">
+        <f t="shared" si="20"/>
+        <v>13500</v>
+      </c>
+      <c r="U68">
         <f>VLOOKUP(T68,LookupTables!$E$2:$F$18,2)</f>
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:21" ht="38.25" x14ac:dyDescent="0.2">
@@ -6552,7 +6551,7 @@
       <c r="B69">
         <v>8</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="2" t="s">
         <v>86</v>
       </c>
       <c r="D69">
@@ -6561,69 +6560,69 @@
       <c r="E69">
         <v>2000</v>
       </c>
-      <c r="F69" s="2">
-        <f>VLOOKUP(Data!B12,LookupTables!$A$2:$C$11,3)</f>
-        <v>250</v>
+      <c r="F69" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>50000</v>
       </c>
       <c r="G69">
         <f>VLOOKUP(F69,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H69">
-        <f>F69/2</f>
-        <v>125</v>
-      </c>
-      <c r="I69" s="3">
+        <f t="shared" si="14"/>
+        <v>25000</v>
+      </c>
+      <c r="I69">
         <f>VLOOKUP(H69,LookupTables!$E$2:$F$18,2)</f>
-        <v>1</v>
-      </c>
-      <c r="J69" s="2">
-        <f>F69+D69</f>
-        <v>1250</v>
+        <v>31</v>
+      </c>
+      <c r="J69" s="1">
+        <f t="shared" si="15"/>
+        <v>51000</v>
       </c>
       <c r="K69">
         <f>VLOOKUP(J69,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="L69">
-        <f>J69/2</f>
-        <v>625</v>
-      </c>
-      <c r="M69" s="3">
+        <f t="shared" si="16"/>
+        <v>25500</v>
+      </c>
+      <c r="M69">
         <f>VLOOKUP(L69,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="N69">
-        <f>F69/2+D69</f>
-        <v>1125</v>
-      </c>
-      <c r="O69" s="3">
+        <f t="shared" si="17"/>
+        <v>26000</v>
+      </c>
+      <c r="O69">
         <f>VLOOKUP(N69,LookupTables!$E$2:$F$18,2)</f>
-        <v>9</v>
-      </c>
-      <c r="P69" s="2">
-        <f>F69+E69+D69</f>
-        <v>3250</v>
+        <v>31</v>
+      </c>
+      <c r="P69" s="1">
+        <f t="shared" si="18"/>
+        <v>53000</v>
       </c>
       <c r="Q69">
         <f>VLOOKUP(P69,LookupTables!$E$2:$F$18,2)</f>
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="R69">
-        <f>P69/2</f>
-        <v>1625</v>
-      </c>
-      <c r="S69" s="3">
+        <f t="shared" si="19"/>
+        <v>26500</v>
+      </c>
+      <c r="S69">
         <f>VLOOKUP(R69,LookupTables!$E$2:$F$18,2)</f>
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="T69">
-        <f>F69/2+E69+D69</f>
-        <v>3125</v>
-      </c>
-      <c r="U69" s="3">
+        <f t="shared" si="20"/>
+        <v>28000</v>
+      </c>
+      <c r="U69">
         <f>VLOOKUP(T69,LookupTables!$E$2:$F$18,2)</f>
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.2">
@@ -6633,7 +6632,7 @@
       <c r="B70">
         <v>8</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="2" t="s">
         <v>105</v>
       </c>
       <c r="D70">
@@ -6642,69 +6641,69 @@
       <c r="E70">
         <v>1000</v>
       </c>
-      <c r="F70" s="2">
-        <f>VLOOKUP(Data!B31,LookupTables!$A$2:$C$11,3)</f>
-        <v>2500</v>
+      <c r="F70" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>50000</v>
       </c>
       <c r="G70">
         <f>VLOOKUP(F70,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H70">
-        <f>F70/2</f>
-        <v>1250</v>
-      </c>
-      <c r="I70" s="3">
+        <f t="shared" si="14"/>
+        <v>25000</v>
+      </c>
+      <c r="I70">
         <f>VLOOKUP(H70,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
-      </c>
-      <c r="J70" s="2">
-        <f>F70+D70</f>
-        <v>2500</v>
+        <v>31</v>
+      </c>
+      <c r="J70" s="1">
+        <f t="shared" si="15"/>
+        <v>50000</v>
       </c>
       <c r="K70">
         <f>VLOOKUP(J70,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="L70">
-        <f>J70/2</f>
-        <v>1250</v>
-      </c>
-      <c r="M70" s="3">
+        <f t="shared" si="16"/>
+        <v>25000</v>
+      </c>
+      <c r="M70">
         <f>VLOOKUP(L70,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="N70">
-        <f>F70/2+D70</f>
-        <v>1250</v>
-      </c>
-      <c r="O70" s="3">
+        <f t="shared" si="17"/>
+        <v>25000</v>
+      </c>
+      <c r="O70">
         <f>VLOOKUP(N70,LookupTables!$E$2:$F$18,2)</f>
-        <v>11</v>
-      </c>
-      <c r="P70" s="2">
-        <f>F70+E70+D70</f>
-        <v>3500</v>
+        <v>31</v>
+      </c>
+      <c r="P70" s="1">
+        <f t="shared" si="18"/>
+        <v>51000</v>
       </c>
       <c r="Q70">
         <f>VLOOKUP(P70,LookupTables!$E$2:$F$18,2)</f>
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="R70">
-        <f>P70/2</f>
-        <v>1750</v>
-      </c>
-      <c r="S70" s="3">
+        <f t="shared" si="19"/>
+        <v>25500</v>
+      </c>
+      <c r="S70">
         <f>VLOOKUP(R70,LookupTables!$E$2:$F$18,2)</f>
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="T70">
-        <f>F70/2+E70+D70</f>
-        <v>2250</v>
-      </c>
-      <c r="U70" s="3">
+        <f t="shared" si="20"/>
+        <v>26000</v>
+      </c>
+      <c r="U70">
         <f>VLOOKUP(T70,LookupTables!$E$2:$F$18,2)</f>
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
@@ -6714,7 +6713,7 @@
       <c r="B71">
         <v>9</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D71">
@@ -6723,69 +6722,69 @@
       <c r="E71">
         <v>0</v>
       </c>
-      <c r="F71" s="2">
-        <f>VLOOKUP(Data!B5,LookupTables!$A$2:$C$11,3)</f>
-        <v>25</v>
+      <c r="F71" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>250000</v>
       </c>
       <c r="G71">
         <f>VLOOKUP(F71,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H71">
-        <f>F71/2</f>
-        <v>12.5</v>
-      </c>
-      <c r="I71" s="3">
+        <f t="shared" si="14"/>
+        <v>125000</v>
+      </c>
+      <c r="I71">
         <f>VLOOKUP(H71,LookupTables!$E$2:$F$18,2)</f>
-        <v>0</v>
-      </c>
-      <c r="J71" s="2">
-        <f>F71+D71</f>
-        <v>1125</v>
+        <v>31</v>
+      </c>
+      <c r="J71" s="1">
+        <f t="shared" si="15"/>
+        <v>251100</v>
       </c>
       <c r="K71">
         <f>VLOOKUP(J71,LookupTables!$E$2:$F$18,2)</f>
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="L71">
-        <f>J71/2</f>
-        <v>562.5</v>
-      </c>
-      <c r="M71" s="3">
+        <f t="shared" si="16"/>
+        <v>125550</v>
+      </c>
+      <c r="M71">
         <f>VLOOKUP(L71,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="N71">
-        <f>F71/2+D71</f>
-        <v>1112.5</v>
-      </c>
-      <c r="O71" s="3">
+        <f t="shared" si="17"/>
+        <v>126100</v>
+      </c>
+      <c r="O71">
         <f>VLOOKUP(N71,LookupTables!$E$2:$F$18,2)</f>
-        <v>9</v>
-      </c>
-      <c r="P71" s="2">
-        <f>F71+E71+D71</f>
-        <v>1125</v>
+        <v>31</v>
+      </c>
+      <c r="P71" s="1">
+        <f t="shared" si="18"/>
+        <v>251100</v>
       </c>
       <c r="Q71">
         <f>VLOOKUP(P71,LookupTables!$E$2:$F$18,2)</f>
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="R71">
-        <f>P71/2</f>
-        <v>562.5</v>
-      </c>
-      <c r="S71" s="3">
+        <f t="shared" si="19"/>
+        <v>125550</v>
+      </c>
+      <c r="S71">
         <f>VLOOKUP(R71,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="T71">
-        <f>F71/2+E71+D71</f>
-        <v>1112.5</v>
-      </c>
-      <c r="U71" s="3">
+        <f t="shared" si="20"/>
+        <v>126100</v>
+      </c>
+      <c r="U71">
         <f>VLOOKUP(T71,LookupTables!$E$2:$F$18,2)</f>
-        <v>9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.2">
@@ -6795,7 +6794,7 @@
       <c r="B72">
         <v>9</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="2" t="s">
         <v>99</v>
       </c>
       <c r="D72">
@@ -6804,69 +6803,69 @@
       <c r="E72">
         <v>5000</v>
       </c>
-      <c r="F72" s="2">
-        <f>VLOOKUP(Data!B25,LookupTables!$A$2:$C$11,3)</f>
-        <v>500</v>
+      <c r="F72" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>250000</v>
       </c>
       <c r="G72">
         <f>VLOOKUP(F72,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="H72">
-        <f>F72/2</f>
-        <v>250</v>
-      </c>
-      <c r="I72" s="3">
+        <f t="shared" si="14"/>
+        <v>125000</v>
+      </c>
+      <c r="I72">
         <f>VLOOKUP(H72,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
-      </c>
-      <c r="J72" s="2">
-        <f>F72+D72</f>
-        <v>500</v>
+        <v>31</v>
+      </c>
+      <c r="J72" s="1">
+        <f t="shared" si="15"/>
+        <v>250000</v>
       </c>
       <c r="K72">
         <f>VLOOKUP(J72,LookupTables!$E$2:$F$18,2)</f>
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="L72">
-        <f>J72/2</f>
-        <v>250</v>
-      </c>
-      <c r="M72" s="3">
+        <f t="shared" si="16"/>
+        <v>125000</v>
+      </c>
+      <c r="M72">
         <f>VLOOKUP(L72,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="N72">
-        <f>F72/2+D72</f>
-        <v>250</v>
-      </c>
-      <c r="O72" s="3">
+        <f t="shared" si="17"/>
+        <v>125000</v>
+      </c>
+      <c r="O72">
         <f>VLOOKUP(N72,LookupTables!$E$2:$F$18,2)</f>
-        <v>3</v>
-      </c>
-      <c r="P72" s="2">
-        <f>F72+E72+D72</f>
-        <v>5500</v>
+        <v>31</v>
+      </c>
+      <c r="P72" s="1">
+        <f t="shared" si="18"/>
+        <v>255000</v>
       </c>
       <c r="Q72">
         <f>VLOOKUP(P72,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="R72">
-        <f>P72/2</f>
-        <v>2750</v>
-      </c>
-      <c r="S72" s="3">
+        <f t="shared" si="19"/>
+        <v>127500</v>
+      </c>
+      <c r="S72">
         <f>VLOOKUP(R72,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="T72">
-        <f>F72/2+E72+D72</f>
-        <v>5250</v>
-      </c>
-      <c r="U72" s="3">
+        <f t="shared" si="20"/>
+        <v>130000</v>
+      </c>
+      <c r="U72">
         <f>VLOOKUP(T72,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.2">
@@ -6876,7 +6875,7 @@
       <c r="B73">
         <v>9</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C73" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D73">
@@ -6885,69 +6884,69 @@
       <c r="E73">
         <v>5000</v>
       </c>
-      <c r="F73" s="2">
-        <f>VLOOKUP(Data!B35,LookupTables!$A$2:$C$11,3)</f>
-        <v>5000</v>
+      <c r="F73" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>250000</v>
       </c>
       <c r="G73">
         <f>VLOOKUP(F73,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H73">
-        <f>F73/2</f>
-        <v>2500</v>
-      </c>
-      <c r="I73" s="3">
+        <f t="shared" si="14"/>
+        <v>125000</v>
+      </c>
+      <c r="I73">
         <f>VLOOKUP(H73,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="J73" s="2">
-        <f>F73+D73</f>
-        <v>5000</v>
+        <v>31</v>
+      </c>
+      <c r="J73" s="1">
+        <f t="shared" si="15"/>
+        <v>250000</v>
       </c>
       <c r="K73">
         <f>VLOOKUP(J73,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="L73">
-        <f>J73/2</f>
-        <v>2500</v>
-      </c>
-      <c r="M73" s="3">
+        <f t="shared" si="16"/>
+        <v>125000</v>
+      </c>
+      <c r="M73">
         <f>VLOOKUP(L73,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="N73">
-        <f>F73/2+D73</f>
-        <v>2500</v>
-      </c>
-      <c r="O73" s="3">
+        <f t="shared" si="17"/>
+        <v>125000</v>
+      </c>
+      <c r="O73">
         <f>VLOOKUP(N73,LookupTables!$E$2:$F$18,2)</f>
-        <v>17</v>
-      </c>
-      <c r="P73" s="2">
-        <f>F73+E73+D73</f>
-        <v>10000</v>
+        <v>31</v>
+      </c>
+      <c r="P73" s="1">
+        <f t="shared" si="18"/>
+        <v>255000</v>
       </c>
       <c r="Q73">
         <f>VLOOKUP(P73,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="R73">
-        <f>P73/2</f>
-        <v>5000</v>
-      </c>
-      <c r="S73" s="3">
+        <f t="shared" si="19"/>
+        <v>127500</v>
+      </c>
+      <c r="S73">
         <f>VLOOKUP(R73,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="T73">
-        <f>F73/2+E73+D73</f>
-        <v>7500</v>
-      </c>
-      <c r="U73" s="3">
+        <f t="shared" si="20"/>
+        <v>130000</v>
+      </c>
+      <c r="U73">
         <f>VLOOKUP(T73,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.2">
@@ -6957,7 +6956,7 @@
       <c r="B74">
         <v>9</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="2" t="s">
         <v>130</v>
       </c>
       <c r="D74">
@@ -6966,69 +6965,69 @@
       <c r="E74">
         <v>1500</v>
       </c>
-      <c r="F74" s="2">
-        <f>VLOOKUP(Data!B56,LookupTables!$A$2:$C$11,3)</f>
-        <v>15000</v>
+      <c r="F74" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
+        <v>250000</v>
       </c>
       <c r="G74">
         <f>VLOOKUP(F74,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H74">
-        <f>F74/2</f>
-        <v>7500</v>
-      </c>
-      <c r="I74" s="3">
+        <f t="shared" si="14"/>
+        <v>125000</v>
+      </c>
+      <c r="I74">
         <f>VLOOKUP(H74,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="J74" s="2">
-        <f>F74+D74</f>
-        <v>15000</v>
+        <v>31</v>
+      </c>
+      <c r="J74" s="1">
+        <f t="shared" si="15"/>
+        <v>250000</v>
       </c>
       <c r="K74">
         <f>VLOOKUP(J74,LookupTables!$E$2:$F$18,2)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L74">
-        <f>J74/2</f>
-        <v>7500</v>
-      </c>
-      <c r="M74" s="3">
+        <f t="shared" si="16"/>
+        <v>125000</v>
+      </c>
+      <c r="M74">
         <f>VLOOKUP(L74,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="N74">
-        <f>F74/2+D74</f>
-        <v>7500</v>
-      </c>
-      <c r="O74" s="3">
+        <f t="shared" si="17"/>
+        <v>125000</v>
+      </c>
+      <c r="O74">
         <f>VLOOKUP(N74,LookupTables!$E$2:$F$18,2)</f>
-        <v>23</v>
-      </c>
-      <c r="P74" s="2">
-        <f>F74+E74+D74</f>
-        <v>16500</v>
+        <v>31</v>
+      </c>
+      <c r="P74" s="1">
+        <f t="shared" si="18"/>
+        <v>251500</v>
       </c>
       <c r="Q74">
         <f>VLOOKUP(P74,LookupTables!$E$2:$F$18,2)</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R74">
-        <f>P74/2</f>
-        <v>8250</v>
-      </c>
-      <c r="S74" s="3">
+        <f t="shared" si="19"/>
+        <v>125750</v>
+      </c>
+      <c r="S74">
         <f>VLOOKUP(R74,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="T74">
-        <f>F74/2+E74+D74</f>
-        <v>9000</v>
-      </c>
-      <c r="U74" s="3">
+        <f t="shared" si="20"/>
+        <v>126500</v>
+      </c>
+      <c r="U74">
         <f>VLOOKUP(T74,LookupTables!$E$2:$F$18,2)</f>
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.2">
@@ -7038,7 +7037,7 @@
       <c r="B75">
         <v>9</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="2" t="s">
         <v>145</v>
       </c>
       <c r="D75">
@@ -7047,8 +7046,8 @@
       <c r="E75">
         <v>0</v>
       </c>
-      <c r="F75" s="2">
-        <f>VLOOKUP(Data!B73,LookupTables!$A$2:$C$11,3)</f>
+      <c r="F75" s="1">
+        <f>VLOOKUP(Table3[[#This Row],[Level]],LookupTables!$A$2:$C$11,3)</f>
         <v>250000</v>
       </c>
       <c r="G75">
@@ -7056,15 +7055,15 @@
         <v>31</v>
       </c>
       <c r="H75">
-        <f>F75/2</f>
+        <f t="shared" si="14"/>
         <v>125000</v>
       </c>
-      <c r="I75" s="3">
+      <c r="I75">
         <f>VLOOKUP(H75,LookupTables!$E$2:$F$18,2)</f>
         <v>31</v>
       </c>
-      <c r="J75" s="2">
-        <f>F75+D75</f>
+      <c r="J75" s="1">
+        <f t="shared" si="15"/>
         <v>275000</v>
       </c>
       <c r="K75">
@@ -7072,23 +7071,23 @@
         <v>31</v>
       </c>
       <c r="L75">
-        <f>J75/2</f>
+        <f t="shared" si="16"/>
         <v>137500</v>
       </c>
-      <c r="M75" s="3">
+      <c r="M75">
         <f>VLOOKUP(L75,LookupTables!$E$2:$F$18,2)</f>
         <v>31</v>
       </c>
       <c r="N75">
-        <f>F75/2+D75</f>
+        <f t="shared" si="17"/>
         <v>150000</v>
       </c>
-      <c r="O75" s="3">
+      <c r="O75">
         <f>VLOOKUP(N75,LookupTables!$E$2:$F$18,2)</f>
         <v>31</v>
       </c>
-      <c r="P75" s="2">
-        <f>F75+E75+D75</f>
+      <c r="P75" s="1">
+        <f t="shared" si="18"/>
         <v>275000</v>
       </c>
       <c r="Q75">
@@ -7096,18 +7095,18 @@
         <v>31</v>
       </c>
       <c r="R75">
-        <f>P75/2</f>
+        <f t="shared" si="19"/>
         <v>137500</v>
       </c>
-      <c r="S75" s="3">
+      <c r="S75">
         <f>VLOOKUP(R75,LookupTables!$E$2:$F$18,2)</f>
         <v>31</v>
       </c>
       <c r="T75">
-        <f>F75/2+E75+D75</f>
+        <f t="shared" si="20"/>
         <v>150000</v>
       </c>
-      <c r="U75" s="3">
+      <c r="U75">
         <f>VLOOKUP(T75,LookupTables!$E$2:$F$18,2)</f>
         <v>31</v>
       </c>

--- a/Spellscrolls/RulesApplicationExample.xlsx
+++ b/Spellscrolls/RulesApplicationExample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentmdh-my.sharepoint.com/personal/abs21004_student_mdu_se/Documents/RPG/Return to Farlorret/Spellscrolls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:8000000b_{ACBF3D38-1FC0-483D-A450-C22652F997C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90181123-EA38-4667-838F-1BC51CA9E710}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:8000000b_{ACBF3D38-1FC0-483D-A450-C22652F997C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A07481DD-1553-4F04-877E-D16AE434A0A1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{712B6D23-A449-45FD-8B49-149B6453368A}"/>
   </bookViews>
@@ -558,12 +558,6 @@
     <t>Time3</t>
   </si>
   <si>
-    <t>Cost4</t>
-  </si>
-  <si>
-    <t>Time5</t>
-  </si>
-  <si>
     <t>Cost Full 50%6</t>
   </si>
   <si>
@@ -574,6 +568,12 @@
   </si>
   <si>
     <t>Time Base 50%9</t>
+  </si>
+  <si>
+    <t>Time2</t>
+  </si>
+  <si>
+    <t>Cost3</t>
   </si>
 </sst>
 </file>
@@ -708,7 +708,7 @@
     <tableColumn id="10" xr3:uid="{5892B10C-4DCB-41F5-B0FC-11D32C656413}" name="Cost2" dataDxfId="1">
       <calculatedColumnFormula>F3+D3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{0823276B-1A68-4883-A7B9-5D905CCE9550}" name="Time3">
+    <tableColumn id="11" xr3:uid="{0823276B-1A68-4883-A7B9-5D905CCE9550}" name="Time2">
       <calculatedColumnFormula>VLOOKUP(J3,LookupTables!$E$2:$F$18,2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{97FEEFB9-6837-4F09-AA32-951B98318D2E}" name="Cost Full 50%">
@@ -723,10 +723,10 @@
     <tableColumn id="15" xr3:uid="{E3014532-18B2-4A87-8462-846199E14AA4}" name="Time Base 50%">
       <calculatedColumnFormula>VLOOKUP(N3,LookupTables!$E$2:$F$18,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{4807FE2B-5FD9-48A9-84B3-B9E2AC68546B}" name="Cost4" dataDxfId="0">
+    <tableColumn id="16" xr3:uid="{4807FE2B-5FD9-48A9-84B3-B9E2AC68546B}" name="Cost3" dataDxfId="0">
       <calculatedColumnFormula>F3+E3+D3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{6A5A75C7-5428-45E9-BF4B-8ED505B086F0}" name="Time5">
+    <tableColumn id="17" xr3:uid="{6A5A75C7-5428-45E9-BF4B-8ED505B086F0}" name="Time3">
       <calculatedColumnFormula>VLOOKUP(P3,LookupTables!$E$2:$F$18,2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="18" xr3:uid="{3695E0A5-A934-4C61-B4E8-0EDD6B04A86D}" name="Cost Full 50%6">
@@ -1106,10 +1106,10 @@
     <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" customWidth="1"/>
     <col min="19" max="19" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.7109375" customWidth="1"/>
+    <col min="21" max="21" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
@@ -1168,7 +1168,7 @@
         <v>172</v>
       </c>
       <c r="K2" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L2" t="s">
         <v>164</v>
@@ -1183,22 +1183,22 @@
         <v>167</v>
       </c>
       <c r="P2" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>173</v>
+      </c>
+      <c r="R2" t="s">
         <v>174</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>175</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>176</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
         <v>177</v>
-      </c>
-      <c r="T2" t="s">
-        <v>178</v>
-      </c>
-      <c r="U2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
